--- a/최종산출물/2. WBS/[2조] WBS(현대이지웰_최종프로젝트).xlsx
+++ b/최종산출물/2. WBS/[2조] WBS(현대이지웰_최종프로젝트).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\공부\hotdog\hotdogdoc\최종산출물\2. WBS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC1A61F-89A4-47AF-956F-F4E0EAD57A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341C4949-1440-4793-B62A-A2E5EC9F185B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="96">
   <si>
     <t>[K-Digital] 현대이지웰 과정 WBS양식 (예시 양식일 뿐, 다른 양식으로 사용하셔도 됩니다)</t>
   </si>
@@ -115,9 +115,6 @@
     <t>정인혁</t>
   </si>
   <si>
-    <t>프로젝트 기본세팅/라우팅/상태관리(Zustand)/공통 UI</t>
-  </si>
-  <si>
     <t>인증 화면(회원/로그인) + 토큰 유지/만료 처리</t>
   </si>
   <si>
@@ -133,401 +130,195 @@
     <t>접근성 점검(키보드/포커스/라벨/대비) + 개선</t>
   </si>
   <si>
-    <t>전원</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>프로젝트 보고서 작성</t>
+  </si>
+  <si>
+    <t>프로젝트 PPT 제작</t>
+  </si>
+  <si>
+    <t>프로젝트 발표</t>
+  </si>
+  <si>
+    <t>WBS/요구사항/정책(POL-01~05) 초안 확정</t>
+  </si>
+  <si>
+    <t>주간 회의록/수행일지 운영</t>
+  </si>
+  <si>
+    <t>이지수, 전이레</t>
+  </si>
+  <si>
+    <t>트러블 슈팅 운영</t>
   </si>
   <si>
     <t>프로젝트 수행</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>WBS/요구사항/정책(POL-01~05) 초안 확정</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>주제 선정 및 기획</t>
+  </si>
+  <si>
+    <t>주제 탐색 리서치</t>
+  </si>
+  <si>
+    <t>벤치마킹 선례(레퍼런스) 리서치</t>
+  </si>
+  <si>
+    <t>프로토타입 생성 및 기초 설계 수립</t>
   </si>
   <si>
     <t>API 명세 v1/Endpoint 정리(요구사항 정의서 기반)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인 프로토타입 개발</t>
+  </si>
+  <si>
+    <t>ERD v1 + Oracle 스키마 완성</t>
+  </si>
+  <si>
+    <t>100%%</t>
+  </si>
+  <si>
+    <t>이지수, 정인혁</t>
+  </si>
+  <si>
+    <t>사용자 인증(P0)</t>
+  </si>
+  <si>
+    <t>접근성 체크리스트 적용 기준 수립</t>
+  </si>
+  <si>
+    <t>회원가입/로그인/JWT/로그아웃</t>
+  </si>
+  <si>
+    <t>비밀번호 찾기(P1)</t>
+  </si>
+  <si>
+    <t>소셜 OAuth2(P1)</t>
+  </si>
+  <si>
+    <t>상품 목록/이커머스(P0)</t>
   </si>
   <si>
     <t>상품 카테고리/목록/검색</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품 상세</t>
+  </si>
+  <si>
+    <t>가중치/노출순위 로직</t>
+  </si>
+  <si>
+    <t>메인 추천(태그 기반 + 품절 제외)</t>
+  </si>
+  <si>
+    <t>전이레, 정인혁</t>
+  </si>
+  <si>
+    <t>북마크/리뷰/인기검색어(P1)</t>
+  </si>
+  <si>
+    <t>장바구니 + DB 동기화(로그인 유저)</t>
+  </si>
+  <si>
+    <t>주문서/주문 생성</t>
   </si>
   <si>
     <t>결제 처리(토스/무통장)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>배송지 저장(P2)</t>
+  </si>
+  <si>
+    <t>마이페이지(P0)</t>
+  </si>
+  <si>
+    <t>프로필 수정/탈퇴</t>
+  </si>
+  <si>
+    <t>구매내역/상세/취소내역</t>
+  </si>
+  <si>
+    <t>북마크 관리(우선순위 낮음)</t>
+  </si>
+  <si>
+    <t>관리자 페이지(P0)</t>
+  </si>
+  <si>
+    <t>관리자 사용자 상태관리</t>
+  </si>
+  <si>
+    <t>관리자 상품 등록/수정/삭제</t>
+  </si>
+  <si>
+    <t>메타태그 관리</t>
+  </si>
+  <si>
+    <t>고객센터(P2)</t>
+  </si>
+  <si>
+    <t>FAQ</t>
+  </si>
+  <si>
+    <t>1:1 문의 게시판</t>
+  </si>
+  <si>
+    <t>시스템 흐름</t>
+  </si>
+  <si>
+    <t>프로젝트 기본세팅</t>
+  </si>
+  <si>
+    <t>정인혁, 전이레</t>
+  </si>
+  <si>
+    <t>라우팅/상태관리(Zustand)/공통 UI</t>
+  </si>
+  <si>
+    <t>김선철, 정인혁, 전이레</t>
+  </si>
+  <si>
+    <t>마이페이지/관리자 UI(핵심 화면 위주)</t>
+  </si>
+  <si>
+    <t>접근성 엔지니어링</t>
+  </si>
+  <si>
+    <t>README/최종 ERD/API/데모 시나리오</t>
+  </si>
+  <si>
+    <t>프런트/백엔드 연동</t>
+  </si>
+  <si>
+    <t>예외처리/검증/에러</t>
+  </si>
+  <si>
+    <t>예외 / 검증 / 에러 알림 UI</t>
+  </si>
+  <si>
+    <t>공통 에러 응답/알림 처리</t>
+  </si>
+  <si>
+    <t>에러 코드 표준화</t>
   </si>
   <si>
     <t>최종 리허설/발표(경진대회)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>주제 선정 및 기획</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>주제 탐색 리서치</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>주간 회의록/수행일지 운영</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>이지수, 전이레</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>트러블 슈팅 운영</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>10주</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>9주</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1주</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>벤치마킹 선례(레퍼런스) 리서치</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ERD v1 + Oracle 스키마 초안</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>김선철, 정인혁</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>접근성 체크리스트 적용 기준 수립</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로토타입 생성 및 기초 설계 수립</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>이지수</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>회원가입/로그인/JWT/로그아웃</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>접근성 중심의 상품중계 복지 쇼핑몰 (3040 직장인 큐레이션)</t>
   </si>
   <si>
     <t>미정</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>가중치/노출순위 로직</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인 추천(태그 기반 + 품절 제외)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로젝트 보고서 작성</t>
-  </si>
-  <si>
-    <t>프로젝트 PPT 제작</t>
-  </si>
-  <si>
-    <t>프로젝트 발표</t>
-  </si>
-  <si>
-    <t>전이레, 정인혁</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>마이페이지/관리자 UI(핵심 화면 위주)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>시스템 흐름</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>README/최종 ERD/API/데모 시나리오</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>상품 상세</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>정인혁</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>장바구니 + DB 동기화(로그인 유저)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>주문서/주문 생성</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>FAQ</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:1 문의 게시판</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>김선철</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>김선철, 정인혁, 전이레</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>메타태그 관리</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>북마크 관리(우선순위 낮음)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로필 수정/탈퇴</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>구매내역/상세/취소내역</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>배송지 저장(P2)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>관리자 사용자 상태관리</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>관리자 상품 등록/수정/삭제</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>사용자 인증(P0)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>비밀번호 찾기(P1)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>소셜 OAuth2(P1)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>상품 목록/이커머스(P0)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>마이페이지(P0)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>관리자 페이지(P0)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>북마크/리뷰/인기검색어(P1)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>고객센터(P2)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>예외처리/검증/에러</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>프런트/백엔드 연동</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>에러 코드 표준화</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>공통 에러 응답/알림 처리</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>예외 / 검증 / 에러 알림 UI</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>접근성</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>중심의</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>상품중계</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>복지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>쇼핑몰</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (3040 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>직장인을 대상으로한 맞춤</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>큐레이션 쇼핑몰</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="m&quot;/&quot;d"/>
+    <numFmt numFmtId="182" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -588,21 +379,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF0070C0"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="나눔고딕"/>
@@ -618,23 +394,33 @@
       <charset val="129"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Malgun Gothic"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Malgun Gothic"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -661,68 +447,29 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor rgb="FFD9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor rgb="FFFFCC00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor rgb="FFFFCC00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor rgb="FFFCE5CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor rgb="FFFBE4D5"/>
+        <fgColor rgb="FFFFD965"/>
+        <bgColor rgb="FFFFD965"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor rgb="FFFBE4D5"/>
+        <bgColor theme="0"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -775,33 +522,31 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
@@ -810,12 +555,12 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -823,26 +568,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -851,121 +590,118 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1183,135 +919,135 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB1014"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="11" customWidth="1"/>
-    <col min="2" max="2" width="46.75" style="11" customWidth="1"/>
-    <col min="3" max="3" width="5.375" style="11" customWidth="1"/>
-    <col min="4" max="4" width="4.5" style="11" customWidth="1"/>
-    <col min="5" max="6" width="12.125" style="11" customWidth="1"/>
-    <col min="7" max="7" width="18.75" style="11" customWidth="1"/>
-    <col min="8" max="8" width="4.375" style="11" customWidth="1"/>
-    <col min="9" max="28" width="4.5" style="11" customWidth="1"/>
+    <col min="1" max="1" width="13.5" style="8" customWidth="1"/>
+    <col min="2" max="2" width="46.75" style="8" customWidth="1"/>
+    <col min="3" max="3" width="5.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="4.5" style="8" customWidth="1"/>
+    <col min="5" max="6" width="12.125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="18.75" style="8" customWidth="1"/>
+    <col min="8" max="8" width="4.375" style="8" customWidth="1"/>
+    <col min="9" max="28" width="4.5" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="47"/>
-      <c r="Y1" s="48"/>
-      <c r="Z1" s="48"/>
-      <c r="AA1" s="48"/>
-      <c r="AB1" s="48"/>
-    </row>
-    <row r="2" spans="1:28" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="12"/>
+    </row>
+    <row r="2" spans="1:28" ht="38.25" customHeight="1">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-    </row>
-    <row r="3" spans="1:28" s="8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+    </row>
+    <row r="3" spans="1:28" s="6" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="C3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="52" t="s">
-        <v>97</v>
-      </c>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="46"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="46"/>
-      <c r="P3" s="46"/>
-      <c r="Q3" s="46"/>
-      <c r="R3" s="46"/>
-      <c r="S3" s="46"/>
-      <c r="T3" s="46"/>
-      <c r="U3" s="46"/>
-      <c r="V3" s="46"/>
-      <c r="W3" s="46"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="7"/>
-    </row>
-    <row r="4" spans="1:28" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="44" t="s">
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+    </row>
+    <row r="4" spans="1:28" ht="13.5" customHeight="1">
+      <c r="A4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="44" t="s">
+      <c r="E4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="44" t="s">
+      <c r="F4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="44" t="s">
+      <c r="G4" s="15" t="s">
         <v>11</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -1356,5650 +1092,5748 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:28" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="45"/>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="9">
+    <row r="5" spans="1:28" ht="13.5" customHeight="1">
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="7">
         <v>46134</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="7">
         <v>46141</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="7">
         <v>46148</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="7">
         <v>46155</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="7">
         <v>46162</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="7">
         <v>46169</v>
       </c>
-      <c r="N5" s="9">
+      <c r="N5" s="7">
         <v>46176</v>
       </c>
-      <c r="O5" s="9">
+      <c r="O5" s="7">
         <v>46183</v>
       </c>
-      <c r="P5" s="9">
+      <c r="P5" s="7">
         <v>46190</v>
       </c>
-      <c r="Q5" s="9">
+      <c r="Q5" s="7">
         <v>46197</v>
       </c>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="40" t="s">
+    <row r="6" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A6" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="24">
         <v>0</v>
       </c>
       <c r="D6" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="26">
         <v>46134</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="26">
         <v>45404</v>
       </c>
-      <c r="G6" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="22"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="15"/>
-      <c r="R6" s="15"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="15"/>
-      <c r="U6" s="15"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="15"/>
-    </row>
-    <row r="7" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="40"/>
-      <c r="B7" s="12" t="s">
+      <c r="G6" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="28"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="29"/>
+      <c r="W6" s="29"/>
+    </row>
+    <row r="7" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A7" s="30"/>
+      <c r="B7" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="24">
         <v>1</v>
       </c>
       <c r="D7" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="26">
         <v>46135</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="26">
         <v>46136</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="15"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="15"/>
-      <c r="S7" s="15"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="15"/>
-      <c r="V7" s="15"/>
-      <c r="W7" s="15"/>
-    </row>
-    <row r="8" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="40"/>
-      <c r="B8" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="13">
+      <c r="H7" s="28"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="29"/>
+      <c r="W7" s="29"/>
+    </row>
+    <row r="8" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A8" s="30"/>
+      <c r="B8" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="24">
         <v>0</v>
       </c>
       <c r="D8" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="26">
         <v>46134</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="26">
         <v>46192</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="28"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="29"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="29"/>
+      <c r="W8" s="29"/>
+    </row>
+    <row r="9" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A9" s="21"/>
+      <c r="B9" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="24">
+        <v>0</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="26">
+        <v>46139</v>
+      </c>
+      <c r="F9" s="26">
+        <v>46196</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+      <c r="W9" s="29"/>
+    </row>
+    <row r="10" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A10" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="29"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="29"/>
+      <c r="W10" s="29"/>
+    </row>
+    <row r="11" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A11" s="36"/>
+      <c r="B11" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="24">
+        <v>1</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="26">
+        <v>46134</v>
+      </c>
+      <c r="F11" s="26">
+        <v>46134</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="28"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="29"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="29"/>
+      <c r="W11" s="29"/>
+    </row>
+    <row r="12" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A12" s="36"/>
+      <c r="B12" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="24">
+        <v>1</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="26">
+        <v>46135</v>
+      </c>
+      <c r="F12" s="26">
+        <v>46135</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="28"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="29"/>
+      <c r="T12" s="29"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="29"/>
+      <c r="W12" s="29"/>
+    </row>
+    <row r="13" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A13" s="36"/>
+      <c r="B13" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="22"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="15"/>
-      <c r="O8" s="15"/>
-      <c r="P8" s="14"/>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="15"/>
-      <c r="S8" s="15"/>
-      <c r="T8" s="15"/>
-      <c r="U8" s="15"/>
-      <c r="V8" s="15"/>
-      <c r="W8" s="15"/>
-    </row>
-    <row r="9" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="40"/>
-      <c r="B9" s="12" t="s">
+      <c r="C13" s="24"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="29"/>
+      <c r="W13" s="29"/>
+    </row>
+    <row r="14" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A14" s="36"/>
+      <c r="B14" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="24">
+        <v>1</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="26">
+        <v>46136</v>
+      </c>
+      <c r="F14" s="26">
+        <v>46136</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="28"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+      <c r="W14" s="29"/>
+    </row>
+    <row r="15" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A15" s="36"/>
+      <c r="B15" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="13">
-        <v>0</v>
-      </c>
-      <c r="D9" s="25" t="s">
+      <c r="C15" s="24">
+        <v>1</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="26">
+        <v>46135</v>
+      </c>
+      <c r="F15" s="26">
+        <v>46136</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="28"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+      <c r="W15" s="29"/>
+    </row>
+    <row r="16" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A16" s="36"/>
+      <c r="B16" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="24">
+        <v>1</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="26">
+        <v>46139</v>
+      </c>
+      <c r="F16" s="26">
+        <v>46139</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="28"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="29"/>
+      <c r="W16" s="29"/>
+    </row>
+    <row r="17" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A17" s="36"/>
+      <c r="B17" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="35">
+      <c r="C17" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="26">
+        <v>46135</v>
+      </c>
+      <c r="F17" s="26">
         <v>46139</v>
       </c>
-      <c r="F9" s="35">
-        <v>46196</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="14"/>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
-      <c r="S9" s="15"/>
-      <c r="T9" s="15"/>
-      <c r="U9" s="15"/>
-      <c r="V9" s="15"/>
-      <c r="W9" s="15"/>
-    </row>
-    <row r="10" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
-      <c r="O10" s="15"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="15"/>
-      <c r="S10" s="15"/>
-      <c r="T10" s="15"/>
-      <c r="U10" s="15"/>
-      <c r="V10" s="15"/>
-      <c r="W10" s="15"/>
-    </row>
-    <row r="11" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="42"/>
-      <c r="B11" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="13">
-        <v>1</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="35">
-        <v>46134</v>
-      </c>
-      <c r="F11" s="35">
-        <v>46134</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="22"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
-      <c r="T11" s="15"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="15"/>
-    </row>
-    <row r="12" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="42"/>
-      <c r="B12" s="17" t="s">
+      <c r="G17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="13">
-        <v>1</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="35">
-        <v>46135</v>
-      </c>
-      <c r="F12" s="35">
-        <v>46135</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="H12" s="22"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="15"/>
-    </row>
-    <row r="13" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="42"/>
-      <c r="B13" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="15"/>
-    </row>
-    <row r="14" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="42"/>
-      <c r="B14" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="35">
-        <v>46136</v>
-      </c>
-      <c r="F14" s="35">
-        <v>46136</v>
-      </c>
-      <c r="G14" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="H14" s="22"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="15"/>
-      <c r="U14" s="15"/>
-      <c r="V14" s="15"/>
-      <c r="W14" s="15"/>
-    </row>
-    <row r="15" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="42"/>
-      <c r="B15" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="35">
-        <v>46135</v>
-      </c>
-      <c r="F15" s="35">
-        <v>46136</v>
-      </c>
-      <c r="G15" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="15"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="15"/>
-      <c r="V15" s="15"/>
-      <c r="W15" s="15"/>
-    </row>
-    <row r="16" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="42"/>
-      <c r="B16" s="18" t="s">
+      <c r="H17" s="28"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="29"/>
+      <c r="W17" s="29"/>
+    </row>
+    <row r="18" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A18" s="36"/>
+      <c r="B18" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="35">
-        <v>46135</v>
-      </c>
-      <c r="F16" s="35">
-        <v>46149</v>
-      </c>
-      <c r="G16" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-    </row>
-    <row r="17" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="42"/>
-      <c r="B17" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="15"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="15"/>
-      <c r="W17" s="15"/>
-    </row>
-    <row r="18" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="42"/>
-      <c r="B18" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="13">
-        <v>0</v>
-      </c>
-      <c r="D18" s="25"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="34"/>
       <c r="E18" s="35"/>
       <c r="F18" s="35"/>
-      <c r="G18" s="26" t="s">
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="29"/>
+      <c r="W18" s="29"/>
+    </row>
+    <row r="19" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A19" s="36"/>
+      <c r="B19" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="24">
+        <v>0</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="26">
+        <v>46139</v>
+      </c>
+      <c r="F19" s="26">
+        <v>46139</v>
+      </c>
+      <c r="G19" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="14"/>
-      <c r="V18" s="14"/>
-      <c r="W18" s="14"/>
-    </row>
-    <row r="19" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="42"/>
-      <c r="B19" s="24" t="s">
+      <c r="H19" s="28"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="29"/>
+      <c r="W19" s="29"/>
+    </row>
+    <row r="20" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A20" s="36"/>
+      <c r="B20" s="38" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="24">
+        <v>0</v>
+      </c>
+      <c r="D20" s="25"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="29"/>
+    </row>
+    <row r="21" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A21" s="36"/>
+      <c r="B21" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="24">
+        <v>0</v>
+      </c>
+      <c r="D21" s="25"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29"/>
+      <c r="N21" s="29"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="29"/>
+      <c r="R21" s="29"/>
+      <c r="S21" s="29"/>
+      <c r="T21" s="29"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="29"/>
+      <c r="W21" s="29"/>
+    </row>
+    <row r="22" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A22" s="36"/>
+      <c r="B22" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="24">
+        <v>0</v>
+      </c>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29"/>
+      <c r="N22" s="29"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="29"/>
+      <c r="Q22" s="29"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="29"/>
+      <c r="W22" s="29"/>
+    </row>
+    <row r="23" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A23" s="36"/>
+      <c r="B23" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="13">
-        <v>0</v>
-      </c>
-      <c r="D19" s="25"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="14"/>
-    </row>
-    <row r="20" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="42"/>
-      <c r="B20" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" s="13">
-        <v>0</v>
-      </c>
-      <c r="D20" s="25"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-    </row>
-    <row r="21" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="42"/>
-      <c r="B21" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" s="13">
-        <v>0</v>
-      </c>
-      <c r="D21" s="25"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-    </row>
-    <row r="22" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="42"/>
-      <c r="B22" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
-    </row>
-    <row r="23" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="42"/>
-      <c r="B23" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="13">
-        <v>0</v>
-      </c>
-      <c r="D23" s="25"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="34"/>
       <c r="E23" s="35"/>
       <c r="F23" s="35"/>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="29"/>
+    </row>
+    <row r="24" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A24" s="36"/>
+      <c r="B24" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="24">
+        <v>0</v>
+      </c>
+      <c r="D24" s="25"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="15"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="15"/>
-      <c r="R23" s="15"/>
-      <c r="S23" s="15"/>
-      <c r="T23" s="15"/>
-      <c r="U23" s="15"/>
-      <c r="V23" s="15"/>
-      <c r="W23" s="15"/>
-    </row>
-    <row r="24" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="42"/>
-      <c r="B24" s="24" t="s">
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="29"/>
+      <c r="W24" s="29"/>
+    </row>
+    <row r="25" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A25" s="36"/>
+      <c r="B25" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="24">
+        <v>0</v>
+      </c>
+      <c r="D25" s="25"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="29"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+      <c r="W25" s="29"/>
+    </row>
+    <row r="26" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A26" s="36"/>
+      <c r="B26" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="24">
+        <v>0</v>
+      </c>
+      <c r="D26" s="25"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+      <c r="W26" s="29"/>
+    </row>
+    <row r="27" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A27" s="36"/>
+      <c r="B27" s="38" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="24">
+        <v>0</v>
+      </c>
+      <c r="D27" s="25"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="29"/>
+      <c r="W27" s="29"/>
+    </row>
+    <row r="28" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A28" s="36"/>
+      <c r="B28" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="24">
+        <v>0</v>
+      </c>
+      <c r="D28" s="25"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+      <c r="W28" s="29"/>
+    </row>
+    <row r="29" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A29" s="36"/>
+      <c r="B29" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="24">
+        <v>0</v>
+      </c>
+      <c r="D29" s="25"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+    </row>
+    <row r="30" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A30" s="36"/>
+      <c r="B30" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="24">
+        <v>0</v>
+      </c>
+      <c r="D30" s="25"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="29"/>
+      <c r="W30" s="29"/>
+    </row>
+    <row r="31" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A31" s="36"/>
+      <c r="B31" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="24">
+        <v>0</v>
+      </c>
+      <c r="D31" s="25"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="29"/>
+      <c r="Q31" s="29"/>
+      <c r="R31" s="29"/>
+      <c r="S31" s="29"/>
+      <c r="T31" s="29"/>
+      <c r="U31" s="29"/>
+      <c r="V31" s="29"/>
+      <c r="W31" s="29"/>
+    </row>
+    <row r="32" spans="1:23" ht="17.25" customHeight="1">
+      <c r="A32" s="36"/>
+      <c r="B32" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="24">
+        <v>0</v>
+      </c>
+      <c r="D32" s="25"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="29"/>
+      <c r="T32" s="29"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="29"/>
+      <c r="W32" s="29"/>
+    </row>
+    <row r="33" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A33" s="36"/>
+      <c r="B33" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="13">
-        <v>0</v>
-      </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="15"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-    </row>
-    <row r="25" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="42"/>
-      <c r="B25" s="24" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="13">
-        <v>0</v>
-      </c>
-      <c r="D25" s="25"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="14"/>
-      <c r="R25" s="14"/>
-      <c r="S25" s="14"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="14"/>
-      <c r="V25" s="14"/>
-      <c r="W25" s="14"/>
-    </row>
-    <row r="26" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="42"/>
-      <c r="B26" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="13">
-        <v>0</v>
-      </c>
-      <c r="D26" s="25"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="H26" s="15"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="15"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="14"/>
-      <c r="R26" s="14"/>
-      <c r="S26" s="14"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="14"/>
-      <c r="V26" s="14"/>
-      <c r="W26" s="14"/>
-    </row>
-    <row r="27" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="42"/>
-      <c r="B27" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" s="13">
-        <v>0</v>
-      </c>
-      <c r="D27" s="25"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
-      <c r="R27" s="15"/>
-      <c r="S27" s="15"/>
-      <c r="T27" s="15"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="15"/>
-      <c r="W27" s="15"/>
-    </row>
-    <row r="28" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="42"/>
-      <c r="B28" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="13">
-        <v>0</v>
-      </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
-      <c r="O28" s="15"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="15"/>
-      <c r="R28" s="14"/>
-      <c r="S28" s="14"/>
-      <c r="T28" s="14"/>
-      <c r="U28" s="14"/>
-      <c r="V28" s="14"/>
-      <c r="W28" s="14"/>
-    </row>
-    <row r="29" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="42"/>
-      <c r="B29" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="13">
-        <v>0</v>
-      </c>
-      <c r="D29" s="25"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="H29" s="15"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="15"/>
-      <c r="R29" s="14"/>
-      <c r="S29" s="14"/>
-      <c r="T29" s="14"/>
-      <c r="U29" s="14"/>
-      <c r="V29" s="14"/>
-      <c r="W29" s="14"/>
-    </row>
-    <row r="30" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="42"/>
-      <c r="B30" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="13">
-        <v>0</v>
-      </c>
-      <c r="D30" s="25"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="H30" s="15"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="15"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="15"/>
-      <c r="R30" s="15"/>
-      <c r="S30" s="15"/>
-      <c r="T30" s="15"/>
-      <c r="U30" s="15"/>
-      <c r="V30" s="15"/>
-      <c r="W30" s="15"/>
-    </row>
-    <row r="31" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="42"/>
-      <c r="B31" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" s="13">
-        <v>0</v>
-      </c>
-      <c r="D31" s="25"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="15"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="15"/>
-      <c r="R31" s="15"/>
-      <c r="S31" s="15"/>
-      <c r="T31" s="15"/>
-      <c r="U31" s="15"/>
-      <c r="V31" s="14"/>
-      <c r="W31" s="14"/>
-    </row>
-    <row r="32" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="42"/>
-      <c r="B32" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="15"/>
-      <c r="R32" s="15"/>
-      <c r="S32" s="15"/>
-      <c r="T32" s="15"/>
-      <c r="U32" s="15"/>
-      <c r="V32" s="14"/>
-      <c r="W32" s="14"/>
-    </row>
-    <row r="33" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="42"/>
-      <c r="B33" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="13">
-        <v>0</v>
-      </c>
-      <c r="D33" s="25"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="34"/>
       <c r="E33" s="35"/>
       <c r="F33" s="35"/>
-      <c r="G33" s="26" t="s">
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="29"/>
+      <c r="N33" s="29"/>
+      <c r="O33" s="29"/>
+      <c r="P33" s="29"/>
+      <c r="Q33" s="29"/>
+      <c r="R33" s="29"/>
+      <c r="S33" s="29"/>
+      <c r="T33" s="29"/>
+      <c r="U33" s="29"/>
+      <c r="V33" s="29"/>
+      <c r="W33" s="29"/>
+    </row>
+    <row r="34" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A34" s="36"/>
+      <c r="B34" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="24">
+        <v>0</v>
+      </c>
+      <c r="D34" s="25"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15"/>
-      <c r="R33" s="15"/>
-      <c r="S33" s="15"/>
-      <c r="T33" s="15"/>
-      <c r="U33" s="15"/>
-      <c r="V33" s="14"/>
-      <c r="W33" s="14"/>
-    </row>
-    <row r="34" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="42"/>
-      <c r="B34" s="24" t="s">
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="29"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="29"/>
+      <c r="Q34" s="29"/>
+      <c r="R34" s="29"/>
+      <c r="S34" s="29"/>
+      <c r="T34" s="29"/>
+      <c r="U34" s="29"/>
+      <c r="V34" s="29"/>
+      <c r="W34" s="29"/>
+    </row>
+    <row r="35" spans="1:28" ht="18" customHeight="1">
+      <c r="A35" s="36"/>
+      <c r="B35" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="24">
+        <v>0</v>
+      </c>
+      <c r="D35" s="25"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="29"/>
+      <c r="N35" s="29"/>
+      <c r="O35" s="29"/>
+      <c r="P35" s="29"/>
+      <c r="Q35" s="29"/>
+      <c r="R35" s="29"/>
+      <c r="S35" s="29"/>
+      <c r="T35" s="29"/>
+      <c r="U35" s="29"/>
+      <c r="V35" s="29"/>
+      <c r="W35" s="29"/>
+    </row>
+    <row r="36" spans="1:28" ht="18" customHeight="1">
+      <c r="A36" s="36"/>
+      <c r="B36" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="24">
+        <v>0</v>
+      </c>
+      <c r="D36" s="27"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="29"/>
+      <c r="N36" s="29"/>
+      <c r="O36" s="29"/>
+      <c r="P36" s="29"/>
+      <c r="Q36" s="29"/>
+      <c r="R36" s="29"/>
+      <c r="S36" s="29"/>
+      <c r="T36" s="29"/>
+      <c r="U36" s="29"/>
+      <c r="V36" s="29"/>
+      <c r="W36" s="29"/>
+    </row>
+    <row r="37" spans="1:28" ht="18.75" customHeight="1">
+      <c r="A37" s="36"/>
+      <c r="B37" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="24"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="29"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="29"/>
+      <c r="W37" s="29"/>
+    </row>
+    <row r="38" spans="1:28" ht="18.75" customHeight="1">
+      <c r="A38" s="36"/>
+      <c r="B38" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="24">
+        <v>0</v>
+      </c>
+      <c r="D38" s="27"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="29"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="29"/>
+      <c r="P38" s="29"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="29"/>
+      <c r="S38" s="29"/>
+      <c r="T38" s="29"/>
+      <c r="U38" s="29"/>
+      <c r="V38" s="29"/>
+      <c r="W38" s="29"/>
+    </row>
+    <row r="39" spans="1:28" ht="18.75" customHeight="1">
+      <c r="A39" s="36"/>
+      <c r="B39" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="24">
+        <v>0</v>
+      </c>
+      <c r="D39" s="27"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="29"/>
+      <c r="N39" s="29"/>
+      <c r="O39" s="29"/>
+      <c r="P39" s="29"/>
+      <c r="Q39" s="29"/>
+      <c r="R39" s="29"/>
+      <c r="S39" s="29"/>
+      <c r="T39" s="29"/>
+      <c r="U39" s="29"/>
+      <c r="V39" s="29"/>
+      <c r="W39" s="29"/>
+    </row>
+    <row r="40" spans="1:28" ht="18.75" customHeight="1">
+      <c r="A40" s="36"/>
+      <c r="B40" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="24">
+        <v>0</v>
+      </c>
+      <c r="D40" s="27"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="29"/>
+      <c r="S40" s="29"/>
+      <c r="T40" s="29"/>
+      <c r="U40" s="29"/>
+      <c r="V40" s="29"/>
+      <c r="W40" s="29"/>
+    </row>
+    <row r="41" spans="1:28" ht="18.75" customHeight="1">
+      <c r="A41" s="36"/>
+      <c r="B41" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" s="24"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="29"/>
+      <c r="L41" s="29"/>
+      <c r="M41" s="29"/>
+      <c r="N41" s="29"/>
+      <c r="O41" s="29"/>
+      <c r="P41" s="29"/>
+      <c r="Q41" s="29"/>
+      <c r="R41" s="29"/>
+      <c r="S41" s="29"/>
+      <c r="T41" s="29"/>
+      <c r="U41" s="29"/>
+      <c r="V41" s="29"/>
+      <c r="W41" s="29"/>
+    </row>
+    <row r="42" spans="1:28" ht="18.75" customHeight="1">
+      <c r="A42" s="36"/>
+      <c r="B42" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" s="24">
+        <v>0</v>
+      </c>
+      <c r="D42" s="27"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="29"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="29"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="29"/>
+      <c r="P42" s="29"/>
+      <c r="Q42" s="29"/>
+      <c r="R42" s="29"/>
+      <c r="S42" s="29"/>
+      <c r="T42" s="29"/>
+      <c r="U42" s="29"/>
+      <c r="V42" s="29"/>
+      <c r="W42" s="29"/>
+    </row>
+    <row r="43" spans="1:28" s="10" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A43" s="36"/>
+      <c r="B43" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" s="24">
+        <v>0</v>
+      </c>
+      <c r="D43" s="27"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="29"/>
+      <c r="S43" s="29"/>
+      <c r="T43" s="29"/>
+      <c r="U43" s="29"/>
+      <c r="V43" s="29"/>
+      <c r="W43" s="29"/>
+      <c r="X43" s="9"/>
+      <c r="Y43" s="9"/>
+      <c r="Z43" s="9"/>
+      <c r="AA43" s="9"/>
+      <c r="AB43" s="9"/>
+    </row>
+    <row r="44" spans="1:28" ht="18.75" customHeight="1">
+      <c r="A44" s="36"/>
+      <c r="B44" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="C34" s="13">
+      <c r="C44" s="24"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
+      <c r="L44" s="42"/>
+      <c r="M44" s="29"/>
+      <c r="N44" s="29"/>
+      <c r="O44" s="29"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="42"/>
+      <c r="R44" s="42"/>
+      <c r="S44" s="42"/>
+      <c r="T44" s="42"/>
+      <c r="U44" s="42"/>
+      <c r="V44" s="42"/>
+      <c r="W44" s="42"/>
+    </row>
+    <row r="45" spans="1:28" ht="18.75" customHeight="1">
+      <c r="A45" s="36"/>
+      <c r="B45" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="C45" s="24">
+        <v>1</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="26">
+        <v>46139</v>
+      </c>
+      <c r="F45" s="26">
+        <v>46139</v>
+      </c>
+      <c r="G45" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="H45" s="28"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="29"/>
+      <c r="N45" s="29"/>
+      <c r="O45" s="29"/>
+      <c r="P45" s="29"/>
+      <c r="Q45" s="29"/>
+      <c r="R45" s="29"/>
+      <c r="S45" s="29"/>
+      <c r="T45" s="29"/>
+      <c r="U45" s="29"/>
+      <c r="V45" s="29"/>
+      <c r="W45" s="29"/>
+    </row>
+    <row r="46" spans="1:28" ht="18.75" customHeight="1">
+      <c r="A46" s="36"/>
+      <c r="B46" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" s="24">
         <v>0</v>
       </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="26" t="s">
+      <c r="D46" s="27"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="15"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="15"/>
-      <c r="Q34" s="15"/>
-      <c r="R34" s="15"/>
-      <c r="S34" s="15"/>
-      <c r="T34" s="15"/>
-      <c r="U34" s="15"/>
-      <c r="V34" s="15"/>
-      <c r="W34" s="15"/>
-    </row>
-    <row r="35" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="42"/>
-      <c r="B35" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" s="13">
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="29"/>
+      <c r="W46" s="29"/>
+    </row>
+    <row r="47" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A47" s="36"/>
+      <c r="B47" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="24">
         <v>0</v>
       </c>
-      <c r="D35" s="23"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="23" t="s">
+      <c r="D47" s="27"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="29"/>
+      <c r="N47" s="29"/>
+      <c r="O47" s="29"/>
+      <c r="P47" s="29"/>
+      <c r="Q47" s="29"/>
+      <c r="R47" s="29"/>
+      <c r="S47" s="29"/>
+      <c r="T47" s="29"/>
+      <c r="U47" s="29"/>
+      <c r="V47" s="29"/>
+      <c r="W47" s="29"/>
+    </row>
+    <row r="48" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A48" s="36"/>
+      <c r="B48" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="24">
+        <v>0</v>
+      </c>
+      <c r="D48" s="27"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="15"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="15"/>
-      <c r="R35" s="15"/>
-      <c r="S35" s="15"/>
-      <c r="T35" s="15"/>
-      <c r="U35" s="15"/>
-      <c r="V35" s="15"/>
-      <c r="W35" s="15"/>
-    </row>
-    <row r="36" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="42"/>
-      <c r="B36" s="34" t="s">
+      <c r="H48" s="29"/>
+      <c r="I48" s="29"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
+      <c r="L48" s="29"/>
+      <c r="M48" s="29"/>
+      <c r="N48" s="29"/>
+      <c r="O48" s="29"/>
+      <c r="P48" s="29"/>
+      <c r="Q48" s="29"/>
+      <c r="R48" s="29"/>
+      <c r="S48" s="29"/>
+      <c r="T48" s="29"/>
+      <c r="U48" s="29"/>
+      <c r="V48" s="29"/>
+      <c r="W48" s="29"/>
+    </row>
+    <row r="49" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A49" s="36"/>
+      <c r="B49" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C49" s="24">
+        <v>0</v>
+      </c>
+      <c r="D49" s="27"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="42"/>
+      <c r="L49" s="42"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29"/>
+      <c r="O49" s="29"/>
+      <c r="P49" s="42"/>
+      <c r="Q49" s="42"/>
+      <c r="R49" s="42"/>
+      <c r="S49" s="42"/>
+      <c r="T49" s="42"/>
+      <c r="U49" s="42"/>
+      <c r="V49" s="42"/>
+      <c r="W49" s="42"/>
+    </row>
+    <row r="50" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A50" s="36"/>
+      <c r="B50" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C50" s="24">
+        <v>0</v>
+      </c>
+      <c r="D50" s="27"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
+      <c r="G50" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H50" s="42"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="42"/>
+      <c r="K50" s="42"/>
+      <c r="L50" s="42"/>
+      <c r="M50" s="42"/>
+      <c r="N50" s="42"/>
+      <c r="O50" s="29"/>
+      <c r="P50" s="29"/>
+      <c r="Q50" s="42"/>
+      <c r="R50" s="42"/>
+      <c r="S50" s="42"/>
+      <c r="T50" s="42"/>
+      <c r="U50" s="42"/>
+      <c r="V50" s="42"/>
+      <c r="W50" s="42"/>
+    </row>
+    <row r="51" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A51" s="36"/>
+      <c r="B51" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" s="24">
+        <v>0</v>
+      </c>
+      <c r="D51" s="27"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H51" s="42"/>
+      <c r="I51" s="42"/>
+      <c r="J51" s="42"/>
+      <c r="K51" s="42"/>
+      <c r="L51" s="42"/>
+      <c r="M51" s="42"/>
+      <c r="N51" s="42"/>
+      <c r="O51" s="29"/>
+      <c r="P51" s="29"/>
+      <c r="Q51" s="42"/>
+      <c r="R51" s="42"/>
+      <c r="S51" s="42"/>
+      <c r="T51" s="42"/>
+      <c r="U51" s="42"/>
+      <c r="V51" s="42"/>
+      <c r="W51" s="42"/>
+    </row>
+    <row r="52" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A52" s="36"/>
+      <c r="B52" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C52" s="24"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="H52" s="42"/>
+      <c r="I52" s="42"/>
+      <c r="J52" s="42"/>
+      <c r="K52" s="42"/>
+      <c r="L52" s="42"/>
+      <c r="M52" s="42"/>
+      <c r="N52" s="42"/>
+      <c r="O52" s="29"/>
+      <c r="P52" s="29"/>
+      <c r="Q52" s="42"/>
+      <c r="R52" s="42"/>
+      <c r="S52" s="42"/>
+      <c r="T52" s="42"/>
+      <c r="U52" s="42"/>
+      <c r="V52" s="42"/>
+      <c r="W52" s="42"/>
+    </row>
+    <row r="53" spans="1:28" s="10" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A53" s="36"/>
+      <c r="B53" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C53" s="24">
+        <v>0</v>
+      </c>
+      <c r="D53" s="27"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="H53" s="42"/>
+      <c r="I53" s="42"/>
+      <c r="J53" s="42"/>
+      <c r="K53" s="42"/>
+      <c r="L53" s="42"/>
+      <c r="M53" s="42"/>
+      <c r="N53" s="42"/>
+      <c r="O53" s="29"/>
+      <c r="P53" s="29"/>
+      <c r="Q53" s="42"/>
+      <c r="R53" s="42"/>
+      <c r="S53" s="42"/>
+      <c r="T53" s="42"/>
+      <c r="U53" s="42"/>
+      <c r="V53" s="42"/>
+      <c r="W53" s="42"/>
+      <c r="X53" s="9"/>
+      <c r="Y53" s="9"/>
+      <c r="Z53" s="9"/>
+      <c r="AA53" s="9"/>
+      <c r="AB53" s="9"/>
+    </row>
+    <row r="54" spans="1:28" s="10" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A54" s="36"/>
+      <c r="B54" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C54" s="24">
+        <v>0</v>
+      </c>
+      <c r="D54" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54" s="26">
+        <v>46134</v>
+      </c>
+      <c r="F54" s="26">
+        <v>46196</v>
+      </c>
+      <c r="G54" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H54" s="28"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="42"/>
+      <c r="K54" s="42"/>
+      <c r="L54" s="42"/>
+      <c r="M54" s="42"/>
+      <c r="N54" s="42"/>
+      <c r="O54" s="42"/>
+      <c r="P54" s="29"/>
+      <c r="Q54" s="29"/>
+      <c r="R54" s="42"/>
+      <c r="S54" s="42"/>
+      <c r="T54" s="42"/>
+      <c r="U54" s="42"/>
+      <c r="V54" s="42"/>
+      <c r="W54" s="42"/>
+      <c r="X54" s="9"/>
+      <c r="Y54" s="9"/>
+      <c r="Z54" s="9"/>
+      <c r="AA54" s="9"/>
+      <c r="AB54" s="9"/>
+    </row>
+    <row r="55" spans="1:28" s="10" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A55" s="36"/>
+      <c r="B55" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" s="24">
+        <v>0</v>
+      </c>
+      <c r="D55" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H55" s="42"/>
+      <c r="I55" s="42"/>
+      <c r="J55" s="42"/>
+      <c r="K55" s="42"/>
+      <c r="L55" s="42"/>
+      <c r="M55" s="42"/>
+      <c r="N55" s="42"/>
+      <c r="O55" s="42"/>
+      <c r="P55" s="29"/>
+      <c r="Q55" s="29"/>
+      <c r="R55" s="42"/>
+      <c r="S55" s="42"/>
+      <c r="T55" s="42"/>
+      <c r="U55" s="42"/>
+      <c r="V55" s="42"/>
+      <c r="W55" s="42"/>
+      <c r="X55" s="9"/>
+      <c r="Y55" s="9"/>
+      <c r="Z55" s="9"/>
+      <c r="AA55" s="9"/>
+      <c r="AB55" s="9"/>
+    </row>
+    <row r="56" spans="1:28" s="10" customFormat="1" ht="17.25" customHeight="1">
+      <c r="A56" s="36"/>
+      <c r="B56" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="15"/>
-      <c r="R36" s="15"/>
-      <c r="S36" s="15"/>
-      <c r="T36" s="15"/>
-      <c r="U36" s="15"/>
-      <c r="V36" s="15"/>
-      <c r="W36" s="15"/>
-    </row>
-    <row r="37" spans="1:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="42"/>
-      <c r="B37" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="C37" s="13">
+      <c r="C56" s="33"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="42"/>
+      <c r="I56" s="42"/>
+      <c r="J56" s="42"/>
+      <c r="K56" s="42"/>
+      <c r="L56" s="42"/>
+      <c r="M56" s="42"/>
+      <c r="N56" s="42"/>
+      <c r="O56" s="42"/>
+      <c r="P56" s="29"/>
+      <c r="Q56" s="29"/>
+      <c r="R56" s="42"/>
+      <c r="S56" s="42"/>
+      <c r="T56" s="42"/>
+      <c r="U56" s="42"/>
+      <c r="V56" s="42"/>
+      <c r="W56" s="42"/>
+      <c r="X56" s="9"/>
+      <c r="Y56" s="9"/>
+      <c r="Z56" s="9"/>
+      <c r="AA56" s="9"/>
+      <c r="AB56" s="9"/>
+    </row>
+    <row r="57" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A57" s="36"/>
+      <c r="B57" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" s="43"/>
+      <c r="D57" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H57" s="42"/>
+      <c r="I57" s="42"/>
+      <c r="J57" s="42"/>
+      <c r="K57" s="42"/>
+      <c r="L57" s="42"/>
+      <c r="M57" s="42"/>
+      <c r="N57" s="42"/>
+      <c r="O57" s="42"/>
+      <c r="P57" s="29"/>
+      <c r="Q57" s="29"/>
+      <c r="R57" s="42"/>
+      <c r="S57" s="42"/>
+      <c r="T57" s="42"/>
+      <c r="U57" s="42"/>
+      <c r="V57" s="42"/>
+      <c r="W57" s="42"/>
+    </row>
+    <row r="58" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A58" s="36"/>
+      <c r="B58" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C58" s="43"/>
+      <c r="D58" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H58" s="42"/>
+      <c r="I58" s="42"/>
+      <c r="J58" s="42"/>
+      <c r="K58" s="42"/>
+      <c r="L58" s="42"/>
+      <c r="M58" s="42"/>
+      <c r="N58" s="42"/>
+      <c r="O58" s="42"/>
+      <c r="P58" s="29"/>
+      <c r="Q58" s="29"/>
+      <c r="R58" s="42"/>
+      <c r="S58" s="42"/>
+      <c r="T58" s="42"/>
+      <c r="U58" s="42"/>
+      <c r="V58" s="42"/>
+      <c r="W58" s="42"/>
+    </row>
+    <row r="59" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A59" s="36"/>
+      <c r="B59" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C59" s="43"/>
+      <c r="D59" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H59" s="42"/>
+      <c r="I59" s="42"/>
+      <c r="J59" s="42"/>
+      <c r="K59" s="42"/>
+      <c r="L59" s="42"/>
+      <c r="M59" s="42"/>
+      <c r="N59" s="42"/>
+      <c r="O59" s="42"/>
+      <c r="P59" s="29"/>
+      <c r="Q59" s="29"/>
+      <c r="R59" s="42"/>
+      <c r="S59" s="42"/>
+      <c r="T59" s="42"/>
+      <c r="U59" s="42"/>
+      <c r="V59" s="42"/>
+      <c r="W59" s="42"/>
+    </row>
+    <row r="60" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A60" s="36"/>
+      <c r="B60" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" s="24">
         <v>0</v>
       </c>
-      <c r="D37" s="23"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="15"/>
-      <c r="O37" s="15"/>
-      <c r="P37" s="15"/>
-      <c r="Q37" s="15"/>
-      <c r="R37" s="15"/>
-      <c r="S37" s="15"/>
-      <c r="T37" s="15"/>
-      <c r="U37" s="15"/>
-      <c r="V37" s="15"/>
-      <c r="W37" s="15"/>
-    </row>
-    <row r="38" spans="1:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="42"/>
-      <c r="B38" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C38" s="13">
+      <c r="D60" s="42"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="42"/>
+      <c r="H60" s="42"/>
+      <c r="I60" s="42"/>
+      <c r="J60" s="42"/>
+      <c r="K60" s="42"/>
+      <c r="L60" s="42"/>
+      <c r="M60" s="42"/>
+      <c r="N60" s="42"/>
+      <c r="O60" s="42"/>
+      <c r="P60" s="42"/>
+      <c r="Q60" s="42"/>
+      <c r="R60" s="42"/>
+      <c r="S60" s="42"/>
+      <c r="T60" s="44"/>
+      <c r="U60" s="44"/>
+      <c r="V60" s="44"/>
+      <c r="W60" s="44"/>
+    </row>
+    <row r="61" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A61" s="36"/>
+      <c r="B61" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="C61" s="24">
         <v>0</v>
       </c>
-      <c r="D38" s="23"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="15"/>
-      <c r="R38" s="15"/>
-      <c r="S38" s="15"/>
-      <c r="T38" s="15"/>
-      <c r="U38" s="15"/>
-      <c r="V38" s="15"/>
-      <c r="W38" s="15"/>
-    </row>
-    <row r="39" spans="1:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="42"/>
-      <c r="B39" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" s="13">
+      <c r="D61" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" s="26">
+        <v>46193</v>
+      </c>
+      <c r="F61" s="26">
+        <v>46196</v>
+      </c>
+      <c r="G61" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H61" s="46"/>
+      <c r="I61" s="46"/>
+      <c r="J61" s="46"/>
+      <c r="K61" s="46"/>
+      <c r="L61" s="46"/>
+      <c r="M61" s="46"/>
+      <c r="N61" s="46"/>
+      <c r="O61" s="46"/>
+      <c r="P61" s="46"/>
+      <c r="Q61" s="46"/>
+      <c r="R61" s="46"/>
+      <c r="S61" s="46"/>
+      <c r="T61" s="46"/>
+      <c r="U61" s="46"/>
+      <c r="V61" s="46"/>
+      <c r="W61" s="46"/>
+    </row>
+    <row r="62" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A62" s="36"/>
+      <c r="B62" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62" s="24">
         <v>0</v>
       </c>
-      <c r="D39" s="23"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H39" s="15"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="15"/>
-      <c r="O39" s="15"/>
-      <c r="P39" s="15"/>
-      <c r="Q39" s="15"/>
-      <c r="R39" s="15"/>
-      <c r="S39" s="15"/>
-      <c r="T39" s="15"/>
-      <c r="U39" s="15"/>
-      <c r="V39" s="15"/>
-      <c r="W39" s="15"/>
-    </row>
-    <row r="40" spans="1:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="42"/>
-      <c r="B40" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="38"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
-      <c r="N40" s="15"/>
-      <c r="O40" s="15"/>
-      <c r="P40" s="15"/>
-      <c r="Q40" s="15"/>
-      <c r="R40" s="15"/>
-      <c r="S40" s="15"/>
-      <c r="T40" s="15"/>
-      <c r="U40" s="15"/>
-      <c r="V40" s="15"/>
-      <c r="W40" s="15"/>
-    </row>
-    <row r="41" spans="1:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="42"/>
-      <c r="B41" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" s="13">
+      <c r="D62" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" s="26">
+        <v>46193</v>
+      </c>
+      <c r="F62" s="26">
+        <v>46196</v>
+      </c>
+      <c r="G62" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="H62" s="46"/>
+      <c r="I62" s="46"/>
+      <c r="J62" s="46"/>
+      <c r="K62" s="46"/>
+      <c r="L62" s="46"/>
+      <c r="M62" s="46"/>
+      <c r="N62" s="46"/>
+      <c r="O62" s="46"/>
+      <c r="P62" s="46"/>
+      <c r="Q62" s="46"/>
+      <c r="R62" s="46"/>
+      <c r="S62" s="46"/>
+      <c r="T62" s="46"/>
+      <c r="U62" s="46"/>
+      <c r="V62" s="46"/>
+      <c r="W62" s="46"/>
+    </row>
+    <row r="63" spans="1:28" ht="17.25" customHeight="1">
+      <c r="A63" s="47"/>
+      <c r="B63" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="C63" s="24">
         <v>0</v>
       </c>
-      <c r="D41" s="23"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="H41" s="15"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
-      <c r="M41" s="15"/>
-      <c r="N41" s="15"/>
-      <c r="O41" s="15"/>
-      <c r="P41" s="15"/>
-      <c r="Q41" s="15"/>
-      <c r="R41" s="15"/>
-      <c r="S41" s="15"/>
-      <c r="T41" s="15"/>
-      <c r="U41" s="15"/>
-      <c r="V41" s="15"/>
-      <c r="W41" s="15"/>
-    </row>
-    <row r="42" spans="1:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="42"/>
-      <c r="B42" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C42" s="13">
-        <v>0</v>
-      </c>
-      <c r="D42" s="23"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="15"/>
-      <c r="N42" s="15"/>
-      <c r="O42" s="15"/>
-      <c r="P42" s="15"/>
-      <c r="Q42" s="15"/>
-      <c r="R42" s="15"/>
-      <c r="S42" s="15"/>
-      <c r="T42" s="15"/>
-      <c r="U42" s="15"/>
-      <c r="V42" s="15"/>
-      <c r="W42" s="15"/>
-    </row>
-    <row r="43" spans="1:28" s="33" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="42"/>
-      <c r="B43" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43" s="13"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="15"/>
-      <c r="N43" s="15"/>
-      <c r="O43" s="15"/>
-      <c r="P43" s="19"/>
-      <c r="Q43" s="19"/>
-      <c r="R43" s="19"/>
-      <c r="S43" s="19"/>
-      <c r="T43" s="19"/>
-      <c r="U43" s="19"/>
-      <c r="V43" s="19"/>
-      <c r="W43" s="19"/>
-      <c r="X43" s="32"/>
-      <c r="Y43" s="32"/>
-      <c r="Z43" s="32"/>
-      <c r="AA43" s="32"/>
-      <c r="AB43" s="32"/>
-    </row>
-    <row r="44" spans="1:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="42"/>
-      <c r="B44" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="13">
-        <v>0</v>
-      </c>
-      <c r="D44" s="23"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
-      <c r="M44" s="15"/>
-      <c r="N44" s="15"/>
-      <c r="O44" s="15"/>
-      <c r="P44" s="15"/>
-      <c r="Q44" s="15"/>
-      <c r="R44" s="15"/>
-      <c r="S44" s="15"/>
-      <c r="T44" s="15"/>
-      <c r="U44" s="15"/>
-      <c r="V44" s="15"/>
-      <c r="W44" s="15"/>
-    </row>
-    <row r="45" spans="1:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="42"/>
-      <c r="B45" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" s="13">
-        <v>0</v>
-      </c>
-      <c r="D45" s="23"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
-      <c r="N45" s="15"/>
-      <c r="O45" s="15"/>
-      <c r="P45" s="15"/>
-      <c r="Q45" s="15"/>
-      <c r="R45" s="15"/>
-      <c r="S45" s="15"/>
-      <c r="T45" s="15"/>
-      <c r="U45" s="15"/>
-      <c r="V45" s="15"/>
-      <c r="W45" s="15"/>
-    </row>
-    <row r="46" spans="1:28" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="42"/>
-      <c r="B46" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C46" s="13">
-        <v>0</v>
-      </c>
-      <c r="D46" s="23"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="15"/>
-      <c r="N46" s="15"/>
-      <c r="O46" s="15"/>
-      <c r="P46" s="15"/>
-      <c r="Q46" s="15"/>
-      <c r="R46" s="15"/>
-      <c r="S46" s="15"/>
-      <c r="T46" s="15"/>
-      <c r="U46" s="15"/>
-      <c r="V46" s="15"/>
-      <c r="W46" s="15"/>
-    </row>
-    <row r="47" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="42"/>
-      <c r="B47" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C47" s="13">
-        <v>0</v>
-      </c>
-      <c r="D47" s="23"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19"/>
-      <c r="K47" s="19"/>
-      <c r="L47" s="19"/>
-      <c r="M47" s="15"/>
-      <c r="N47" s="15"/>
-      <c r="O47" s="15"/>
-      <c r="P47" s="19"/>
-      <c r="Q47" s="19"/>
-      <c r="R47" s="19"/>
-      <c r="S47" s="19"/>
-      <c r="T47" s="19"/>
-      <c r="U47" s="19"/>
-      <c r="V47" s="19"/>
-      <c r="W47" s="19"/>
-    </row>
-    <row r="48" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="42"/>
-      <c r="B48" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C48" s="13">
-        <v>0</v>
-      </c>
-      <c r="D48" s="23"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="H48" s="19"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="19"/>
-      <c r="K48" s="19"/>
-      <c r="L48" s="19"/>
-      <c r="M48" s="19"/>
-      <c r="N48" s="19"/>
-      <c r="O48" s="15"/>
-      <c r="P48" s="15"/>
-      <c r="Q48" s="19"/>
-      <c r="R48" s="19"/>
-      <c r="S48" s="19"/>
-      <c r="T48" s="19"/>
-      <c r="U48" s="19"/>
-      <c r="V48" s="19"/>
-      <c r="W48" s="19"/>
-    </row>
-    <row r="49" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="42"/>
-      <c r="B49" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" s="13">
-        <v>0</v>
-      </c>
-      <c r="D49" s="23"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="H49" s="19"/>
-      <c r="I49" s="19"/>
-      <c r="J49" s="19"/>
-      <c r="K49" s="19"/>
-      <c r="L49" s="19"/>
-      <c r="M49" s="19"/>
-      <c r="N49" s="19"/>
-      <c r="O49" s="15"/>
-      <c r="P49" s="15"/>
-      <c r="Q49" s="19"/>
-      <c r="R49" s="19"/>
-      <c r="S49" s="19"/>
-      <c r="T49" s="19"/>
-      <c r="U49" s="19"/>
-      <c r="V49" s="19"/>
-      <c r="W49" s="19"/>
-    </row>
-    <row r="50" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="42"/>
-      <c r="B50" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C50" s="13">
-        <v>0</v>
-      </c>
-      <c r="D50" s="23"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H50" s="19"/>
-      <c r="I50" s="19"/>
-      <c r="J50" s="19"/>
-      <c r="K50" s="19"/>
-      <c r="L50" s="19"/>
-      <c r="M50" s="19"/>
-      <c r="N50" s="19"/>
-      <c r="O50" s="15"/>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="19"/>
-      <c r="R50" s="19"/>
-      <c r="S50" s="19"/>
-      <c r="T50" s="19"/>
-      <c r="U50" s="19"/>
-      <c r="V50" s="19"/>
-      <c r="W50" s="19"/>
-    </row>
-    <row r="51" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="42"/>
-      <c r="B51" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="C51" s="13">
-        <v>0</v>
-      </c>
-      <c r="D51" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="E51" s="37">
-        <v>46134</v>
-      </c>
-      <c r="F51" s="35">
-        <v>46196</v>
-      </c>
-      <c r="G51" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="H51" s="19"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="19"/>
-      <c r="K51" s="19"/>
-      <c r="L51" s="19"/>
-      <c r="M51" s="19"/>
-      <c r="N51" s="19"/>
-      <c r="O51" s="19"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="15"/>
-      <c r="R51" s="19"/>
-      <c r="S51" s="19"/>
-      <c r="T51" s="19"/>
-      <c r="U51" s="19"/>
-      <c r="V51" s="19"/>
-      <c r="W51" s="19"/>
-    </row>
-    <row r="52" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="42"/>
-      <c r="B52" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C52" s="13">
-        <v>0</v>
-      </c>
-      <c r="D52" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="E52" s="37"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="H52" s="19"/>
-      <c r="I52" s="19"/>
-      <c r="J52" s="19"/>
-      <c r="K52" s="19"/>
-      <c r="L52" s="19"/>
-      <c r="M52" s="19"/>
-      <c r="N52" s="19"/>
-      <c r="O52" s="19"/>
-      <c r="P52" s="15"/>
-      <c r="Q52" s="15"/>
-      <c r="R52" s="19"/>
-      <c r="S52" s="19"/>
-      <c r="T52" s="19"/>
-      <c r="U52" s="19"/>
-      <c r="V52" s="19"/>
-      <c r="W52" s="19"/>
-    </row>
-    <row r="53" spans="1:28" s="33" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="42"/>
-      <c r="B53" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C53" s="28"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="38"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="19"/>
-      <c r="J53" s="19"/>
-      <c r="K53" s="19"/>
-      <c r="L53" s="19"/>
-      <c r="M53" s="19"/>
-      <c r="N53" s="19"/>
-      <c r="O53" s="19"/>
-      <c r="P53" s="15"/>
-      <c r="Q53" s="15"/>
-      <c r="R53" s="19"/>
-      <c r="S53" s="19"/>
-      <c r="T53" s="19"/>
-      <c r="U53" s="19"/>
-      <c r="V53" s="19"/>
-      <c r="W53" s="19"/>
-      <c r="X53" s="32"/>
-      <c r="Y53" s="32"/>
-      <c r="Z53" s="32"/>
-      <c r="AA53" s="32"/>
-      <c r="AB53" s="32"/>
-    </row>
-    <row r="54" spans="1:28" s="33" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="42"/>
-      <c r="B54" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="C54" s="39"/>
-      <c r="D54" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="E54" s="37"/>
-      <c r="F54" s="35"/>
-      <c r="G54" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="H54" s="19"/>
-      <c r="I54" s="19"/>
-      <c r="J54" s="19"/>
-      <c r="K54" s="19"/>
-      <c r="L54" s="19"/>
-      <c r="M54" s="19"/>
-      <c r="N54" s="19"/>
-      <c r="O54" s="19"/>
-      <c r="P54" s="15"/>
-      <c r="Q54" s="15"/>
-      <c r="R54" s="19"/>
-      <c r="S54" s="19"/>
-      <c r="T54" s="19"/>
-      <c r="U54" s="19"/>
-      <c r="V54" s="19"/>
-      <c r="W54" s="19"/>
-      <c r="X54" s="32"/>
-      <c r="Y54" s="32"/>
-      <c r="Z54" s="32"/>
-      <c r="AA54" s="32"/>
-      <c r="AB54" s="32"/>
-    </row>
-    <row r="55" spans="1:28" s="33" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="42"/>
-      <c r="B55" s="23" t="s">
+      <c r="D63" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" s="26">
+        <v>46197</v>
+      </c>
+      <c r="F63" s="26">
+        <v>46197</v>
+      </c>
+      <c r="G63" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="C55" s="39"/>
-      <c r="D55" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="E55" s="37"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="H55" s="19"/>
-      <c r="I55" s="19"/>
-      <c r="J55" s="19"/>
-      <c r="K55" s="19"/>
-      <c r="L55" s="19"/>
-      <c r="M55" s="19"/>
-      <c r="N55" s="19"/>
-      <c r="O55" s="19"/>
-      <c r="P55" s="15"/>
-      <c r="Q55" s="15"/>
-      <c r="R55" s="19"/>
-      <c r="S55" s="19"/>
-      <c r="T55" s="19"/>
-      <c r="U55" s="19"/>
-      <c r="V55" s="19"/>
-      <c r="W55" s="19"/>
-      <c r="X55" s="32"/>
-      <c r="Y55" s="32"/>
-      <c r="Z55" s="32"/>
-      <c r="AA55" s="32"/>
-      <c r="AB55" s="32"/>
-    </row>
-    <row r="56" spans="1:28" s="33" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="42"/>
-      <c r="B56" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C56" s="39"/>
-      <c r="D56" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="E56" s="37"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="H56" s="19"/>
-      <c r="I56" s="19"/>
-      <c r="J56" s="19"/>
-      <c r="K56" s="19"/>
-      <c r="L56" s="19"/>
-      <c r="M56" s="19"/>
-      <c r="N56" s="19"/>
-      <c r="O56" s="19"/>
-      <c r="P56" s="15"/>
-      <c r="Q56" s="15"/>
-      <c r="R56" s="19"/>
-      <c r="S56" s="19"/>
-      <c r="T56" s="19"/>
-      <c r="U56" s="19"/>
-      <c r="V56" s="19"/>
-      <c r="W56" s="19"/>
-      <c r="X56" s="32"/>
-      <c r="Y56" s="32"/>
-      <c r="Z56" s="32"/>
-      <c r="AA56" s="32"/>
-      <c r="AB56" s="32"/>
-    </row>
-    <row r="57" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="42"/>
-      <c r="B57" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="C57" s="13">
-        <v>0</v>
-      </c>
-      <c r="D57" s="19"/>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="19"/>
-      <c r="J57" s="19"/>
-      <c r="K57" s="19"/>
-      <c r="L57" s="19"/>
-      <c r="M57" s="19"/>
-      <c r="N57" s="19"/>
-      <c r="O57" s="19"/>
-      <c r="P57" s="19"/>
-      <c r="Q57" s="19"/>
-      <c r="R57" s="19"/>
-      <c r="S57" s="19"/>
-      <c r="T57" s="20"/>
-      <c r="U57" s="20"/>
-      <c r="V57" s="20"/>
-      <c r="W57" s="20"/>
-    </row>
-    <row r="58" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="42"/>
-      <c r="B58" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="C58" s="13">
-        <v>0</v>
-      </c>
-      <c r="D58" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E58" s="35">
-        <v>46193</v>
-      </c>
-      <c r="F58" s="35">
-        <v>46196</v>
-      </c>
-      <c r="G58" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
-      <c r="J58" s="21"/>
-      <c r="K58" s="21"/>
-      <c r="L58" s="21"/>
-      <c r="M58" s="21"/>
-      <c r="N58" s="21"/>
-      <c r="O58" s="21"/>
-      <c r="P58" s="21"/>
-      <c r="Q58" s="21"/>
-      <c r="R58" s="21"/>
-      <c r="S58" s="21"/>
-      <c r="T58" s="21"/>
-      <c r="U58" s="21"/>
-      <c r="V58" s="21"/>
-      <c r="W58" s="21"/>
-    </row>
-    <row r="59" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="42"/>
-      <c r="B59" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="C59" s="13">
-        <v>0</v>
-      </c>
-      <c r="D59" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E59" s="35">
-        <v>46193</v>
-      </c>
-      <c r="F59" s="35">
-        <v>46196</v>
-      </c>
-      <c r="G59" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="H59" s="21"/>
-      <c r="I59" s="21"/>
-      <c r="J59" s="21"/>
-      <c r="K59" s="21"/>
-      <c r="L59" s="21"/>
-      <c r="M59" s="21"/>
-      <c r="N59" s="21"/>
-      <c r="O59" s="21"/>
-      <c r="P59" s="21"/>
-      <c r="Q59" s="21"/>
-      <c r="R59" s="21"/>
-      <c r="S59" s="21"/>
-      <c r="T59" s="21"/>
-      <c r="U59" s="21"/>
-      <c r="V59" s="21"/>
-      <c r="W59" s="21"/>
-    </row>
-    <row r="60" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="43"/>
-      <c r="B60" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C60" s="13">
-        <v>0</v>
-      </c>
-      <c r="D60" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E60" s="35">
-        <v>46197</v>
-      </c>
-      <c r="F60" s="35">
-        <v>46197</v>
-      </c>
-      <c r="G60" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="H60" s="21"/>
-      <c r="I60" s="21"/>
-      <c r="J60" s="21"/>
-      <c r="K60" s="21"/>
-      <c r="L60" s="21"/>
-      <c r="M60" s="21"/>
-      <c r="N60" s="21"/>
-      <c r="O60" s="21"/>
-      <c r="P60" s="21"/>
-      <c r="Q60" s="21"/>
-      <c r="R60" s="21"/>
-      <c r="S60" s="21"/>
-      <c r="T60" s="21"/>
-      <c r="U60" s="21"/>
-      <c r="V60" s="21"/>
-      <c r="W60" s="21"/>
-    </row>
-    <row r="61" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-    </row>
-    <row r="62" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-    </row>
-    <row r="63" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-    </row>
-    <row r="64" spans="1:28" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H63" s="46"/>
+      <c r="I63" s="46"/>
+      <c r="J63" s="46"/>
+      <c r="K63" s="46"/>
+      <c r="L63" s="46"/>
+      <c r="M63" s="46"/>
+      <c r="N63" s="46"/>
+      <c r="O63" s="46"/>
+      <c r="P63" s="46"/>
+      <c r="Q63" s="46"/>
+      <c r="R63" s="46"/>
+      <c r="S63" s="46"/>
+      <c r="T63" s="46"/>
+      <c r="U63" s="46"/>
+      <c r="V63" s="46"/>
+      <c r="W63" s="46"/>
+    </row>
+    <row r="64" spans="1:28" ht="17.25" customHeight="1">
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="5:6" ht="17.25" customHeight="1">
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="5:6" ht="17.25" customHeight="1">
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="5:6" ht="17.25" customHeight="1">
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="5:6" ht="17.25" customHeight="1">
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="5:6" ht="17.25" customHeight="1">
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="5:6" ht="17.25" customHeight="1">
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="5:6" ht="17.25" customHeight="1">
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="5:6" ht="17.25" customHeight="1">
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="5:6" ht="17.25" customHeight="1">
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="5:6" ht="17.25" customHeight="1">
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
     </row>
-    <row r="75" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="5:6" ht="17.25" customHeight="1">
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
     </row>
-    <row r="76" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="5:6" ht="17.25" customHeight="1">
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="5:6" ht="17.25" customHeight="1">
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
     </row>
-    <row r="78" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="5:6" ht="17.25" customHeight="1">
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="5:6" ht="17.25" customHeight="1">
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="5:6" ht="17.25" customHeight="1">
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
     </row>
-    <row r="81" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="5:6" ht="17.25" customHeight="1">
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
     </row>
-    <row r="82" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="5:6" ht="17.25" customHeight="1">
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
     </row>
-    <row r="83" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="5:6" ht="17.25" customHeight="1">
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
     </row>
-    <row r="84" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="5:6" ht="17.25" customHeight="1">
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
     </row>
-    <row r="85" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="5:6" ht="17.25" customHeight="1">
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
     </row>
-    <row r="86" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="5:6" ht="17.25" customHeight="1">
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
     </row>
-    <row r="87" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="5:6" ht="17.25" customHeight="1">
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
     </row>
-    <row r="88" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="5:6" ht="17.25" customHeight="1">
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
     </row>
-    <row r="89" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="5:6" ht="17.25" customHeight="1">
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
     </row>
-    <row r="90" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="5:6" ht="17.25" customHeight="1">
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="5:6" ht="17.25" customHeight="1">
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
     </row>
-    <row r="92" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="5:6" ht="17.25" customHeight="1">
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="5:6" ht="17.25" customHeight="1">
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="5:6" ht="17.25" customHeight="1">
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="5:6" ht="17.25" customHeight="1">
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
     </row>
-    <row r="96" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="5:6" ht="17.25" customHeight="1">
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
     </row>
-    <row r="97" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="5:6" ht="17.25" customHeight="1">
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
     </row>
-    <row r="98" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="5:6" ht="17.25" customHeight="1">
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
     </row>
-    <row r="99" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="5:6" ht="17.25" customHeight="1">
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
     </row>
-    <row r="100" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="5:6" ht="17.25" customHeight="1">
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
     </row>
-    <row r="101" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="5:6" ht="17.25" customHeight="1">
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
     </row>
-    <row r="102" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="5:6" ht="17.25" customHeight="1">
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
     </row>
-    <row r="103" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="5:6" ht="17.25" customHeight="1">
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
     </row>
-    <row r="104" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="5:6" ht="17.25" customHeight="1">
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
     </row>
-    <row r="105" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="5:6" ht="17.25" customHeight="1">
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
     </row>
-    <row r="106" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="5:6" ht="17.25" customHeight="1">
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
     </row>
-    <row r="107" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="5:6" ht="17.25" customHeight="1">
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
     </row>
-    <row r="108" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="5:6" ht="17.25" customHeight="1">
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
     </row>
-    <row r="109" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="5:6" ht="17.25" customHeight="1">
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
     </row>
-    <row r="110" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="5:6" ht="17.25" customHeight="1">
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
     </row>
-    <row r="111" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="5:6" ht="17.25" customHeight="1">
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
     </row>
-    <row r="112" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="5:6" ht="17.25" customHeight="1">
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
     </row>
-    <row r="113" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="5:6" ht="17.25" customHeight="1">
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
     </row>
-    <row r="114" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="5:6" ht="17.25" customHeight="1">
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
     </row>
-    <row r="115" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="5:6" ht="17.25" customHeight="1">
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
     </row>
-    <row r="116" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="5:6" ht="17.25" customHeight="1">
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
     </row>
-    <row r="117" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="5:6" ht="17.25" customHeight="1">
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
     </row>
-    <row r="118" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="5:6" ht="17.25" customHeight="1">
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
     </row>
-    <row r="119" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="5:6" ht="17.25" customHeight="1">
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
     </row>
-    <row r="120" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="5:6" ht="17.25" customHeight="1">
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
     </row>
-    <row r="121" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="5:6" ht="17.25" customHeight="1">
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
     </row>
-    <row r="122" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="5:6" ht="17.25" customHeight="1">
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
     </row>
-    <row r="123" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="5:6" ht="17.25" customHeight="1">
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
     </row>
-    <row r="124" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="5:6" ht="17.25" customHeight="1">
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
     </row>
-    <row r="125" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="5:6" ht="17.25" customHeight="1">
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
     </row>
-    <row r="126" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="5:6" ht="17.25" customHeight="1">
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
     </row>
-    <row r="127" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="5:6" ht="17.25" customHeight="1">
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
     </row>
-    <row r="128" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="5:6" ht="17.25" customHeight="1">
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
     </row>
-    <row r="129" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="5:6" ht="17.25" customHeight="1">
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
     </row>
-    <row r="130" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="5:6" ht="17.25" customHeight="1">
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
     </row>
-    <row r="131" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="5:6" ht="17.25" customHeight="1">
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
     </row>
-    <row r="132" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="5:6" ht="17.25" customHeight="1">
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
     </row>
-    <row r="133" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="5:6" ht="17.25" customHeight="1">
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
     </row>
-    <row r="134" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="5:6" ht="17.25" customHeight="1">
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
     </row>
-    <row r="135" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="5:6" ht="17.25" customHeight="1">
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
     </row>
-    <row r="136" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="5:6" ht="17.25" customHeight="1">
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
     </row>
-    <row r="137" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="5:6" ht="17.25" customHeight="1">
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
     </row>
-    <row r="138" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="5:6" ht="17.25" customHeight="1">
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
     </row>
-    <row r="139" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="5:6" ht="17.25" customHeight="1">
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
     </row>
-    <row r="140" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="5:6" ht="17.25" customHeight="1">
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
     </row>
-    <row r="141" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="5:6" ht="17.25" customHeight="1">
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
     </row>
-    <row r="142" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="5:6" ht="17.25" customHeight="1">
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
     </row>
-    <row r="143" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="5:6" ht="17.25" customHeight="1">
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
     </row>
-    <row r="144" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="5:6" ht="17.25" customHeight="1">
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
     </row>
-    <row r="145" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="5:6" ht="17.25" customHeight="1">
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
     </row>
-    <row r="146" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="5:6" ht="17.25" customHeight="1">
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
     </row>
-    <row r="147" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="5:6" ht="17.25" customHeight="1">
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
     </row>
-    <row r="148" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="5:6" ht="17.25" customHeight="1">
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
     </row>
-    <row r="149" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="5:6" ht="17.25" customHeight="1">
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
     </row>
-    <row r="150" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="5:6" ht="17.25" customHeight="1">
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
     </row>
-    <row r="151" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="5:6" ht="17.25" customHeight="1">
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
     </row>
-    <row r="152" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="5:6" ht="17.25" customHeight="1">
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
     </row>
-    <row r="153" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="5:6" ht="17.25" customHeight="1">
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
     </row>
-    <row r="154" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="5:6" ht="17.25" customHeight="1">
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
     </row>
-    <row r="155" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="5:6" ht="17.25" customHeight="1">
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
     </row>
-    <row r="156" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="5:6" ht="17.25" customHeight="1">
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
     </row>
-    <row r="157" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="5:6" ht="17.25" customHeight="1">
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
     </row>
-    <row r="158" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="5:6" ht="17.25" customHeight="1">
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
     </row>
-    <row r="159" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="5:6" ht="17.25" customHeight="1">
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
     </row>
-    <row r="160" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="5:6" ht="17.25" customHeight="1">
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
     </row>
-    <row r="161" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="5:6" ht="17.25" customHeight="1">
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
     </row>
-    <row r="162" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="5:6" ht="17.25" customHeight="1">
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
     </row>
-    <row r="163" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="5:6" ht="17.25" customHeight="1">
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
     </row>
-    <row r="164" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="5:6" ht="17.25" customHeight="1">
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
     </row>
-    <row r="165" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="5:6" ht="17.25" customHeight="1">
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
     </row>
-    <row r="166" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="5:6" ht="17.25" customHeight="1">
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
     </row>
-    <row r="167" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="5:6" ht="17.25" customHeight="1">
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
     </row>
-    <row r="168" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="5:6" ht="17.25" customHeight="1">
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
     </row>
-    <row r="169" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="5:6" ht="17.25" customHeight="1">
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
     </row>
-    <row r="170" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="5:6" ht="17.25" customHeight="1">
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
     </row>
-    <row r="171" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="5:6" ht="17.25" customHeight="1">
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
     </row>
-    <row r="172" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="5:6" ht="17.25" customHeight="1">
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
     </row>
-    <row r="173" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="5:6" ht="17.25" customHeight="1">
       <c r="E173" s="1"/>
       <c r="F173" s="1"/>
     </row>
-    <row r="174" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="5:6" ht="17.25" customHeight="1">
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
     </row>
-    <row r="175" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="5:6" ht="17.25" customHeight="1">
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
     </row>
-    <row r="176" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="5:6" ht="17.25" customHeight="1">
       <c r="E176" s="1"/>
       <c r="F176" s="1"/>
     </row>
-    <row r="177" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="5:6" ht="17.25" customHeight="1">
       <c r="E177" s="1"/>
       <c r="F177" s="1"/>
     </row>
-    <row r="178" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="5:6" ht="17.25" customHeight="1">
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
     </row>
-    <row r="179" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="5:6" ht="17.25" customHeight="1">
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
     </row>
-    <row r="180" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="5:6" ht="17.25" customHeight="1">
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
     </row>
-    <row r="181" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="5:6" ht="17.25" customHeight="1">
       <c r="E181" s="1"/>
       <c r="F181" s="1"/>
     </row>
-    <row r="182" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="5:6" ht="17.25" customHeight="1">
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
     </row>
-    <row r="183" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="5:6" ht="17.25" customHeight="1">
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
     </row>
-    <row r="184" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="5:6" ht="17.25" customHeight="1">
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
     </row>
-    <row r="185" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="5:6" ht="17.25" customHeight="1">
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
     </row>
-    <row r="186" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="5:6" ht="17.25" customHeight="1">
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
     </row>
-    <row r="187" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="5:6" ht="17.25" customHeight="1">
       <c r="E187" s="1"/>
       <c r="F187" s="1"/>
     </row>
-    <row r="188" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="5:6" ht="17.25" customHeight="1">
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
     </row>
-    <row r="189" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="5:6" ht="17.25" customHeight="1">
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
     </row>
-    <row r="190" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="5:6" ht="17.25" customHeight="1">
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
     </row>
-    <row r="191" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="5:6" ht="17.25" customHeight="1">
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
     </row>
-    <row r="192" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="5:6" ht="17.25" customHeight="1">
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
     </row>
-    <row r="193" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="5:6" ht="17.25" customHeight="1">
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
     </row>
-    <row r="194" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="5:6" ht="17.25" customHeight="1">
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
     </row>
-    <row r="195" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="5:6" ht="17.25" customHeight="1">
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
     </row>
-    <row r="196" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="5:6" ht="17.25" customHeight="1">
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
     </row>
-    <row r="197" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="5:6" ht="17.25" customHeight="1">
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
     </row>
-    <row r="198" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="5:6" ht="17.25" customHeight="1">
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
     </row>
-    <row r="199" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="5:6" ht="17.25" customHeight="1">
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
     </row>
-    <row r="200" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="5:6" ht="17.25" customHeight="1">
       <c r="E200" s="1"/>
       <c r="F200" s="1"/>
     </row>
-    <row r="201" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="5:6" ht="17.25" customHeight="1">
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
     </row>
-    <row r="202" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="5:6" ht="17.25" customHeight="1">
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
     </row>
-    <row r="203" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="5:6" ht="17.25" customHeight="1">
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
     </row>
-    <row r="204" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="5:6" ht="17.25" customHeight="1">
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
     </row>
-    <row r="205" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="5:6" ht="17.25" customHeight="1">
       <c r="E205" s="1"/>
       <c r="F205" s="1"/>
     </row>
-    <row r="206" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="5:6" ht="17.25" customHeight="1">
       <c r="E206" s="1"/>
       <c r="F206" s="1"/>
     </row>
-    <row r="207" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="5:6" ht="17.25" customHeight="1">
       <c r="E207" s="1"/>
       <c r="F207" s="1"/>
     </row>
-    <row r="208" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="5:6" ht="17.25" customHeight="1">
       <c r="E208" s="1"/>
       <c r="F208" s="1"/>
     </row>
-    <row r="209" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="5:6" ht="17.25" customHeight="1">
       <c r="E209" s="1"/>
       <c r="F209" s="1"/>
     </row>
-    <row r="210" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="5:6" ht="17.25" customHeight="1">
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
     </row>
-    <row r="211" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="5:6" ht="17.25" customHeight="1">
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
     </row>
-    <row r="212" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="5:6" ht="17.25" customHeight="1">
       <c r="E212" s="1"/>
       <c r="F212" s="1"/>
     </row>
-    <row r="213" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="5:6" ht="17.25" customHeight="1">
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
     </row>
-    <row r="214" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="5:6" ht="17.25" customHeight="1">
       <c r="E214" s="1"/>
       <c r="F214" s="1"/>
     </row>
-    <row r="215" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="5:6" ht="17.25" customHeight="1">
       <c r="E215" s="1"/>
       <c r="F215" s="1"/>
     </row>
-    <row r="216" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="5:6" ht="17.25" customHeight="1">
       <c r="E216" s="1"/>
       <c r="F216" s="1"/>
     </row>
-    <row r="217" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="5:6" ht="17.25" customHeight="1">
       <c r="E217" s="1"/>
       <c r="F217" s="1"/>
     </row>
-    <row r="218" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="5:6" ht="17.25" customHeight="1">
       <c r="E218" s="1"/>
       <c r="F218" s="1"/>
     </row>
-    <row r="219" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="5:6" ht="17.25" customHeight="1">
       <c r="E219" s="1"/>
       <c r="F219" s="1"/>
     </row>
-    <row r="220" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="5:6" ht="17.25" customHeight="1">
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
     </row>
-    <row r="221" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="5:6" ht="17.25" customHeight="1">
       <c r="E221" s="1"/>
       <c r="F221" s="1"/>
     </row>
-    <row r="222" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="5:6" ht="17.25" customHeight="1">
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
     </row>
-    <row r="223" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="5:6" ht="17.25" customHeight="1">
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
     </row>
-    <row r="224" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="5:6" ht="17.25" customHeight="1">
       <c r="E224" s="1"/>
       <c r="F224" s="1"/>
     </row>
-    <row r="225" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="5:6" ht="17.25" customHeight="1">
       <c r="E225" s="1"/>
       <c r="F225" s="1"/>
     </row>
-    <row r="226" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="5:6" ht="17.25" customHeight="1">
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
     </row>
-    <row r="227" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="5:6" ht="17.25" customHeight="1">
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
     </row>
-    <row r="228" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="5:6" ht="17.25" customHeight="1">
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
     </row>
-    <row r="229" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="5:6" ht="17.25" customHeight="1">
       <c r="E229" s="1"/>
       <c r="F229" s="1"/>
     </row>
-    <row r="230" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="5:6" ht="17.25" customHeight="1">
       <c r="E230" s="1"/>
       <c r="F230" s="1"/>
     </row>
-    <row r="231" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="5:6" ht="17.25" customHeight="1">
       <c r="E231" s="1"/>
       <c r="F231" s="1"/>
     </row>
-    <row r="232" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="5:6" ht="17.25" customHeight="1">
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
     </row>
-    <row r="233" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="5:6" ht="17.25" customHeight="1">
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
     </row>
-    <row r="234" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="5:6" ht="17.25" customHeight="1">
       <c r="E234" s="1"/>
       <c r="F234" s="1"/>
     </row>
-    <row r="235" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="5:6" ht="17.25" customHeight="1">
       <c r="E235" s="1"/>
       <c r="F235" s="1"/>
     </row>
-    <row r="236" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="5:6" ht="17.25" customHeight="1">
       <c r="E236" s="1"/>
       <c r="F236" s="1"/>
     </row>
-    <row r="237" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="5:6" ht="17.25" customHeight="1">
       <c r="E237" s="1"/>
       <c r="F237" s="1"/>
     </row>
-    <row r="238" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="5:6" ht="17.25" customHeight="1">
       <c r="E238" s="1"/>
       <c r="F238" s="1"/>
     </row>
-    <row r="239" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="5:6" ht="17.25" customHeight="1">
       <c r="E239" s="1"/>
       <c r="F239" s="1"/>
     </row>
-    <row r="240" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="5:6" ht="17.25" customHeight="1">
       <c r="E240" s="1"/>
       <c r="F240" s="1"/>
     </row>
-    <row r="241" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="5:6" ht="17.25" customHeight="1">
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
     </row>
-    <row r="242" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="5:6" ht="17.25" customHeight="1">
       <c r="E242" s="1"/>
       <c r="F242" s="1"/>
     </row>
-    <row r="243" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="5:6" ht="17.25" customHeight="1">
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
     </row>
-    <row r="244" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="5:6" ht="17.25" customHeight="1">
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
     </row>
-    <row r="245" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="5:6" ht="17.25" customHeight="1">
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
     </row>
-    <row r="246" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="5:6" ht="17.25" customHeight="1">
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
     </row>
-    <row r="247" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="5:6" ht="17.25" customHeight="1">
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
     </row>
-    <row r="248" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="5:6" ht="17.25" customHeight="1">
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
     </row>
-    <row r="249" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="5:6" ht="17.25" customHeight="1">
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
     </row>
-    <row r="250" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="5:6" ht="17.25" customHeight="1">
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
     </row>
-    <row r="251" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="5:6" ht="17.25" customHeight="1">
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
     </row>
-    <row r="252" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="5:6" ht="17.25" customHeight="1">
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
     </row>
-    <row r="253" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="5:6" ht="17.25" customHeight="1">
       <c r="E253" s="1"/>
       <c r="F253" s="1"/>
     </row>
-    <row r="254" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="5:6" ht="17.25" customHeight="1">
       <c r="E254" s="1"/>
       <c r="F254" s="1"/>
     </row>
-    <row r="255" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="5:6" ht="17.25" customHeight="1">
       <c r="E255" s="1"/>
       <c r="F255" s="1"/>
     </row>
-    <row r="256" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="5:6" ht="17.25" customHeight="1">
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
     </row>
-    <row r="257" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="5:6" ht="17.25" customHeight="1">
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
     </row>
-    <row r="258" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="5:6" ht="17.25" customHeight="1">
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
     </row>
-    <row r="259" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="5:6" ht="17.25" customHeight="1">
       <c r="E259" s="1"/>
       <c r="F259" s="1"/>
     </row>
-    <row r="260" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="5:6" ht="17.25" customHeight="1">
       <c r="E260" s="1"/>
       <c r="F260" s="1"/>
     </row>
-    <row r="261" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="5:6" ht="17.25" customHeight="1">
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
     </row>
-    <row r="262" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="5:6" ht="17.25" customHeight="1">
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
     </row>
-    <row r="263" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="5:6" ht="17.25" customHeight="1">
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
     </row>
-    <row r="264" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="5:6" ht="17.25" customHeight="1">
       <c r="E264" s="1"/>
       <c r="F264" s="1"/>
     </row>
-    <row r="265" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="5:6" ht="17.25" customHeight="1">
       <c r="E265" s="1"/>
       <c r="F265" s="1"/>
     </row>
-    <row r="266" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="5:6" ht="17.25" customHeight="1">
       <c r="E266" s="1"/>
       <c r="F266" s="1"/>
     </row>
-    <row r="267" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="5:6" ht="17.25" customHeight="1">
       <c r="E267" s="1"/>
       <c r="F267" s="1"/>
     </row>
-    <row r="268" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="5:6" ht="17.25" customHeight="1">
       <c r="E268" s="1"/>
       <c r="F268" s="1"/>
     </row>
-    <row r="269" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="5:6" ht="17.25" customHeight="1">
       <c r="E269" s="1"/>
       <c r="F269" s="1"/>
     </row>
-    <row r="270" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="5:6" ht="17.25" customHeight="1">
       <c r="E270" s="1"/>
       <c r="F270" s="1"/>
     </row>
-    <row r="271" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="5:6" ht="17.25" customHeight="1">
       <c r="E271" s="1"/>
       <c r="F271" s="1"/>
     </row>
-    <row r="272" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="5:6" ht="17.25" customHeight="1">
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
     </row>
-    <row r="273" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="5:6" ht="17.25" customHeight="1">
       <c r="E273" s="1"/>
       <c r="F273" s="1"/>
     </row>
-    <row r="274" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="5:6" ht="17.25" customHeight="1">
       <c r="E274" s="1"/>
       <c r="F274" s="1"/>
     </row>
-    <row r="275" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="5:6" ht="17.25" customHeight="1">
       <c r="E275" s="1"/>
       <c r="F275" s="1"/>
     </row>
-    <row r="276" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="5:6" ht="17.25" customHeight="1">
       <c r="E276" s="1"/>
       <c r="F276" s="1"/>
     </row>
-    <row r="277" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="5:6" ht="17.25" customHeight="1">
       <c r="E277" s="1"/>
       <c r="F277" s="1"/>
     </row>
-    <row r="278" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="5:6" ht="17.25" customHeight="1">
       <c r="E278" s="1"/>
       <c r="F278" s="1"/>
     </row>
-    <row r="279" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="5:6" ht="17.25" customHeight="1">
       <c r="E279" s="1"/>
       <c r="F279" s="1"/>
     </row>
-    <row r="280" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="5:6" ht="17.25" customHeight="1">
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
     </row>
-    <row r="281" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="5:6" ht="17.25" customHeight="1">
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
     </row>
-    <row r="282" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="5:6" ht="17.25" customHeight="1">
       <c r="E282" s="1"/>
       <c r="F282" s="1"/>
     </row>
-    <row r="283" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="5:6" ht="17.25" customHeight="1">
       <c r="E283" s="1"/>
       <c r="F283" s="1"/>
     </row>
-    <row r="284" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="5:6" ht="17.25" customHeight="1">
       <c r="E284" s="1"/>
       <c r="F284" s="1"/>
     </row>
-    <row r="285" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="5:6" ht="17.25" customHeight="1">
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
     </row>
-    <row r="286" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="5:6" ht="17.25" customHeight="1">
       <c r="E286" s="1"/>
       <c r="F286" s="1"/>
     </row>
-    <row r="287" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="5:6" ht="17.25" customHeight="1">
       <c r="E287" s="1"/>
       <c r="F287" s="1"/>
     </row>
-    <row r="288" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="5:6" ht="17.25" customHeight="1">
       <c r="E288" s="1"/>
       <c r="F288" s="1"/>
     </row>
-    <row r="289" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="5:6" ht="17.25" customHeight="1">
       <c r="E289" s="1"/>
       <c r="F289" s="1"/>
     </row>
-    <row r="290" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="5:6" ht="17.25" customHeight="1">
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
     </row>
-    <row r="291" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="5:6" ht="17.25" customHeight="1">
       <c r="E291" s="1"/>
       <c r="F291" s="1"/>
     </row>
-    <row r="292" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="5:6" ht="17.25" customHeight="1">
       <c r="E292" s="1"/>
       <c r="F292" s="1"/>
     </row>
-    <row r="293" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="5:6" ht="17.25" customHeight="1">
       <c r="E293" s="1"/>
       <c r="F293" s="1"/>
     </row>
-    <row r="294" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="5:6" ht="17.25" customHeight="1">
       <c r="E294" s="1"/>
       <c r="F294" s="1"/>
     </row>
-    <row r="295" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="5:6" ht="17.25" customHeight="1">
       <c r="E295" s="1"/>
       <c r="F295" s="1"/>
     </row>
-    <row r="296" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="5:6" ht="17.25" customHeight="1">
       <c r="E296" s="1"/>
       <c r="F296" s="1"/>
     </row>
-    <row r="297" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="5:6" ht="17.25" customHeight="1">
       <c r="E297" s="1"/>
       <c r="F297" s="1"/>
     </row>
-    <row r="298" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="5:6" ht="17.25" customHeight="1">
       <c r="E298" s="1"/>
       <c r="F298" s="1"/>
     </row>
-    <row r="299" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="5:6" ht="17.25" customHeight="1">
       <c r="E299" s="1"/>
       <c r="F299" s="1"/>
     </row>
-    <row r="300" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="5:6" ht="17.25" customHeight="1">
       <c r="E300" s="1"/>
       <c r="F300" s="1"/>
     </row>
-    <row r="301" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="5:6" ht="17.25" customHeight="1">
       <c r="E301" s="1"/>
       <c r="F301" s="1"/>
     </row>
-    <row r="302" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="5:6" ht="17.25" customHeight="1">
       <c r="E302" s="1"/>
       <c r="F302" s="1"/>
     </row>
-    <row r="303" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="5:6" ht="17.25" customHeight="1">
       <c r="E303" s="1"/>
       <c r="F303" s="1"/>
     </row>
-    <row r="304" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="5:6" ht="17.25" customHeight="1">
       <c r="E304" s="1"/>
       <c r="F304" s="1"/>
     </row>
-    <row r="305" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="5:6" ht="17.25" customHeight="1">
       <c r="E305" s="1"/>
       <c r="F305" s="1"/>
     </row>
-    <row r="306" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="5:6" ht="17.25" customHeight="1">
       <c r="E306" s="1"/>
       <c r="F306" s="1"/>
     </row>
-    <row r="307" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="5:6" ht="17.25" customHeight="1">
       <c r="E307" s="1"/>
       <c r="F307" s="1"/>
     </row>
-    <row r="308" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="5:6" ht="17.25" customHeight="1">
       <c r="E308" s="1"/>
       <c r="F308" s="1"/>
     </row>
-    <row r="309" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="5:6" ht="17.25" customHeight="1">
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
     </row>
-    <row r="310" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="5:6" ht="17.25" customHeight="1">
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
     </row>
-    <row r="311" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="5:6" ht="17.25" customHeight="1">
       <c r="E311" s="1"/>
       <c r="F311" s="1"/>
     </row>
-    <row r="312" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="5:6" ht="17.25" customHeight="1">
       <c r="E312" s="1"/>
       <c r="F312" s="1"/>
     </row>
-    <row r="313" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="5:6" ht="17.25" customHeight="1">
       <c r="E313" s="1"/>
       <c r="F313" s="1"/>
     </row>
-    <row r="314" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="5:6" ht="17.25" customHeight="1">
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
     </row>
-    <row r="315" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="5:6" ht="17.25" customHeight="1">
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
     </row>
-    <row r="316" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="5:6" ht="17.25" customHeight="1">
       <c r="E316" s="1"/>
       <c r="F316" s="1"/>
     </row>
-    <row r="317" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="5:6" ht="17.25" customHeight="1">
       <c r="E317" s="1"/>
       <c r="F317" s="1"/>
     </row>
-    <row r="318" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="5:6" ht="17.25" customHeight="1">
       <c r="E318" s="1"/>
       <c r="F318" s="1"/>
     </row>
-    <row r="319" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="5:6" ht="17.25" customHeight="1">
       <c r="E319" s="1"/>
       <c r="F319" s="1"/>
     </row>
-    <row r="320" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="5:6" ht="17.25" customHeight="1">
       <c r="E320" s="1"/>
       <c r="F320" s="1"/>
     </row>
-    <row r="321" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="5:6" ht="17.25" customHeight="1">
       <c r="E321" s="1"/>
       <c r="F321" s="1"/>
     </row>
-    <row r="322" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="5:6" ht="17.25" customHeight="1">
       <c r="E322" s="1"/>
       <c r="F322" s="1"/>
     </row>
-    <row r="323" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="5:6" ht="17.25" customHeight="1">
       <c r="E323" s="1"/>
       <c r="F323" s="1"/>
     </row>
-    <row r="324" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="5:6" ht="17.25" customHeight="1">
       <c r="E324" s="1"/>
       <c r="F324" s="1"/>
     </row>
-    <row r="325" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="5:6" ht="17.25" customHeight="1">
       <c r="E325" s="1"/>
       <c r="F325" s="1"/>
     </row>
-    <row r="326" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="5:6" ht="17.25" customHeight="1">
       <c r="E326" s="1"/>
       <c r="F326" s="1"/>
     </row>
-    <row r="327" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="5:6" ht="17.25" customHeight="1">
       <c r="E327" s="1"/>
       <c r="F327" s="1"/>
     </row>
-    <row r="328" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="5:6" ht="17.25" customHeight="1">
       <c r="E328" s="1"/>
       <c r="F328" s="1"/>
     </row>
-    <row r="329" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="5:6" ht="17.25" customHeight="1">
       <c r="E329" s="1"/>
       <c r="F329" s="1"/>
     </row>
-    <row r="330" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="5:6" ht="17.25" customHeight="1">
       <c r="E330" s="1"/>
       <c r="F330" s="1"/>
     </row>
-    <row r="331" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="5:6" ht="17.25" customHeight="1">
       <c r="E331" s="1"/>
       <c r="F331" s="1"/>
     </row>
-    <row r="332" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="5:6" ht="17.25" customHeight="1">
       <c r="E332" s="1"/>
       <c r="F332" s="1"/>
     </row>
-    <row r="333" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="5:6" ht="17.25" customHeight="1">
       <c r="E333" s="1"/>
       <c r="F333" s="1"/>
     </row>
-    <row r="334" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="5:6" ht="17.25" customHeight="1">
       <c r="E334" s="1"/>
       <c r="F334" s="1"/>
     </row>
-    <row r="335" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="5:6" ht="17.25" customHeight="1">
       <c r="E335" s="1"/>
       <c r="F335" s="1"/>
     </row>
-    <row r="336" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="5:6" ht="17.25" customHeight="1">
       <c r="E336" s="1"/>
       <c r="F336" s="1"/>
     </row>
-    <row r="337" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="5:6" ht="17.25" customHeight="1">
       <c r="E337" s="1"/>
       <c r="F337" s="1"/>
     </row>
-    <row r="338" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="5:6" ht="17.25" customHeight="1">
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
     </row>
-    <row r="339" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="5:6" ht="17.25" customHeight="1">
       <c r="E339" s="1"/>
       <c r="F339" s="1"/>
     </row>
-    <row r="340" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="5:6" ht="17.25" customHeight="1">
       <c r="E340" s="1"/>
       <c r="F340" s="1"/>
     </row>
-    <row r="341" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="5:6" ht="17.25" customHeight="1">
       <c r="E341" s="1"/>
       <c r="F341" s="1"/>
     </row>
-    <row r="342" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="5:6" ht="17.25" customHeight="1">
       <c r="E342" s="1"/>
       <c r="F342" s="1"/>
     </row>
-    <row r="343" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="5:6" ht="17.25" customHeight="1">
       <c r="E343" s="1"/>
       <c r="F343" s="1"/>
     </row>
-    <row r="344" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="5:6" ht="17.25" customHeight="1">
       <c r="E344" s="1"/>
       <c r="F344" s="1"/>
     </row>
-    <row r="345" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="5:6" ht="17.25" customHeight="1">
       <c r="E345" s="1"/>
       <c r="F345" s="1"/>
     </row>
-    <row r="346" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="5:6" ht="17.25" customHeight="1">
       <c r="E346" s="1"/>
       <c r="F346" s="1"/>
     </row>
-    <row r="347" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="5:6" ht="17.25" customHeight="1">
       <c r="E347" s="1"/>
       <c r="F347" s="1"/>
     </row>
-    <row r="348" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="5:6" ht="17.25" customHeight="1">
       <c r="E348" s="1"/>
       <c r="F348" s="1"/>
     </row>
-    <row r="349" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="5:6" ht="17.25" customHeight="1">
       <c r="E349" s="1"/>
       <c r="F349" s="1"/>
     </row>
-    <row r="350" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="5:6" ht="17.25" customHeight="1">
       <c r="E350" s="1"/>
       <c r="F350" s="1"/>
     </row>
-    <row r="351" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="5:6" ht="17.25" customHeight="1">
       <c r="E351" s="1"/>
       <c r="F351" s="1"/>
     </row>
-    <row r="352" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="5:6" ht="17.25" customHeight="1">
       <c r="E352" s="1"/>
       <c r="F352" s="1"/>
     </row>
-    <row r="353" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="5:6" ht="17.25" customHeight="1">
       <c r="E353" s="1"/>
       <c r="F353" s="1"/>
     </row>
-    <row r="354" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="5:6" ht="17.25" customHeight="1">
       <c r="E354" s="1"/>
       <c r="F354" s="1"/>
     </row>
-    <row r="355" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="5:6" ht="17.25" customHeight="1">
       <c r="E355" s="1"/>
       <c r="F355" s="1"/>
     </row>
-    <row r="356" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="5:6" ht="17.25" customHeight="1">
       <c r="E356" s="1"/>
       <c r="F356" s="1"/>
     </row>
-    <row r="357" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="5:6" ht="17.25" customHeight="1">
       <c r="E357" s="1"/>
       <c r="F357" s="1"/>
     </row>
-    <row r="358" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="5:6" ht="17.25" customHeight="1">
       <c r="E358" s="1"/>
       <c r="F358" s="1"/>
     </row>
-    <row r="359" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="5:6" ht="17.25" customHeight="1">
       <c r="E359" s="1"/>
       <c r="F359" s="1"/>
     </row>
-    <row r="360" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="5:6" ht="17.25" customHeight="1">
       <c r="E360" s="1"/>
       <c r="F360" s="1"/>
     </row>
-    <row r="361" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="5:6" ht="17.25" customHeight="1">
       <c r="E361" s="1"/>
       <c r="F361" s="1"/>
     </row>
-    <row r="362" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="5:6" ht="17.25" customHeight="1">
       <c r="E362" s="1"/>
       <c r="F362" s="1"/>
     </row>
-    <row r="363" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="5:6" ht="17.25" customHeight="1">
       <c r="E363" s="1"/>
       <c r="F363" s="1"/>
     </row>
-    <row r="364" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="5:6" ht="17.25" customHeight="1">
       <c r="E364" s="1"/>
       <c r="F364" s="1"/>
     </row>
-    <row r="365" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="5:6" ht="17.25" customHeight="1">
       <c r="E365" s="1"/>
       <c r="F365" s="1"/>
     </row>
-    <row r="366" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="5:6" ht="17.25" customHeight="1">
       <c r="E366" s="1"/>
       <c r="F366" s="1"/>
     </row>
-    <row r="367" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="5:6" ht="17.25" customHeight="1">
       <c r="E367" s="1"/>
       <c r="F367" s="1"/>
     </row>
-    <row r="368" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="5:6" ht="17.25" customHeight="1">
       <c r="E368" s="1"/>
       <c r="F368" s="1"/>
     </row>
-    <row r="369" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="5:6" ht="17.25" customHeight="1">
       <c r="E369" s="1"/>
       <c r="F369" s="1"/>
     </row>
-    <row r="370" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="5:6" ht="17.25" customHeight="1">
       <c r="E370" s="1"/>
       <c r="F370" s="1"/>
     </row>
-    <row r="371" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="5:6" ht="17.25" customHeight="1">
       <c r="E371" s="1"/>
       <c r="F371" s="1"/>
     </row>
-    <row r="372" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="5:6" ht="17.25" customHeight="1">
       <c r="E372" s="1"/>
       <c r="F372" s="1"/>
     </row>
-    <row r="373" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="5:6" ht="17.25" customHeight="1">
       <c r="E373" s="1"/>
       <c r="F373" s="1"/>
     </row>
-    <row r="374" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="5:6" ht="17.25" customHeight="1">
       <c r="E374" s="1"/>
       <c r="F374" s="1"/>
     </row>
-    <row r="375" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="5:6" ht="17.25" customHeight="1">
       <c r="E375" s="1"/>
       <c r="F375" s="1"/>
     </row>
-    <row r="376" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="5:6" ht="17.25" customHeight="1">
       <c r="E376" s="1"/>
       <c r="F376" s="1"/>
     </row>
-    <row r="377" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="5:6" ht="17.25" customHeight="1">
       <c r="E377" s="1"/>
       <c r="F377" s="1"/>
     </row>
-    <row r="378" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="5:6" ht="17.25" customHeight="1">
       <c r="E378" s="1"/>
       <c r="F378" s="1"/>
     </row>
-    <row r="379" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="5:6" ht="17.25" customHeight="1">
       <c r="E379" s="1"/>
       <c r="F379" s="1"/>
     </row>
-    <row r="380" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="5:6" ht="17.25" customHeight="1">
       <c r="E380" s="1"/>
       <c r="F380" s="1"/>
     </row>
-    <row r="381" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="5:6" ht="17.25" customHeight="1">
       <c r="E381" s="1"/>
       <c r="F381" s="1"/>
     </row>
-    <row r="382" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="5:6" ht="17.25" customHeight="1">
       <c r="E382" s="1"/>
       <c r="F382" s="1"/>
     </row>
-    <row r="383" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="5:6" ht="17.25" customHeight="1">
       <c r="E383" s="1"/>
       <c r="F383" s="1"/>
     </row>
-    <row r="384" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="5:6" ht="17.25" customHeight="1">
       <c r="E384" s="1"/>
       <c r="F384" s="1"/>
     </row>
-    <row r="385" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="5:6" ht="17.25" customHeight="1">
       <c r="E385" s="1"/>
       <c r="F385" s="1"/>
     </row>
-    <row r="386" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="5:6" ht="17.25" customHeight="1">
       <c r="E386" s="1"/>
       <c r="F386" s="1"/>
     </row>
-    <row r="387" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="5:6" ht="17.25" customHeight="1">
       <c r="E387" s="1"/>
       <c r="F387" s="1"/>
     </row>
-    <row r="388" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="5:6" ht="17.25" customHeight="1">
       <c r="E388" s="1"/>
       <c r="F388" s="1"/>
     </row>
-    <row r="389" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="5:6" ht="17.25" customHeight="1">
       <c r="E389" s="1"/>
       <c r="F389" s="1"/>
     </row>
-    <row r="390" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="5:6" ht="17.25" customHeight="1">
       <c r="E390" s="1"/>
       <c r="F390" s="1"/>
     </row>
-    <row r="391" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="5:6" ht="17.25" customHeight="1">
       <c r="E391" s="1"/>
       <c r="F391" s="1"/>
     </row>
-    <row r="392" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="5:6" ht="17.25" customHeight="1">
       <c r="E392" s="1"/>
       <c r="F392" s="1"/>
     </row>
-    <row r="393" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="5:6" ht="17.25" customHeight="1">
       <c r="E393" s="1"/>
       <c r="F393" s="1"/>
     </row>
-    <row r="394" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="5:6" ht="17.25" customHeight="1">
       <c r="E394" s="1"/>
       <c r="F394" s="1"/>
     </row>
-    <row r="395" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="5:6" ht="17.25" customHeight="1">
       <c r="E395" s="1"/>
       <c r="F395" s="1"/>
     </row>
-    <row r="396" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="5:6" ht="17.25" customHeight="1">
       <c r="E396" s="1"/>
       <c r="F396" s="1"/>
     </row>
-    <row r="397" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="5:6" ht="17.25" customHeight="1">
       <c r="E397" s="1"/>
       <c r="F397" s="1"/>
     </row>
-    <row r="398" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="5:6" ht="17.25" customHeight="1">
       <c r="E398" s="1"/>
       <c r="F398" s="1"/>
     </row>
-    <row r="399" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="5:6" ht="17.25" customHeight="1">
       <c r="E399" s="1"/>
       <c r="F399" s="1"/>
     </row>
-    <row r="400" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="5:6" ht="17.25" customHeight="1">
       <c r="E400" s="1"/>
       <c r="F400" s="1"/>
     </row>
-    <row r="401" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="5:6" ht="17.25" customHeight="1">
       <c r="E401" s="1"/>
       <c r="F401" s="1"/>
     </row>
-    <row r="402" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="5:6" ht="17.25" customHeight="1">
       <c r="E402" s="1"/>
       <c r="F402" s="1"/>
     </row>
-    <row r="403" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="5:6" ht="17.25" customHeight="1">
       <c r="E403" s="1"/>
       <c r="F403" s="1"/>
     </row>
-    <row r="404" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="5:6" ht="17.25" customHeight="1">
       <c r="E404" s="1"/>
       <c r="F404" s="1"/>
     </row>
-    <row r="405" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="5:6" ht="17.25" customHeight="1">
       <c r="E405" s="1"/>
       <c r="F405" s="1"/>
     </row>
-    <row r="406" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="5:6" ht="17.25" customHeight="1">
       <c r="E406" s="1"/>
       <c r="F406" s="1"/>
     </row>
-    <row r="407" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="5:6" ht="17.25" customHeight="1">
       <c r="E407" s="1"/>
       <c r="F407" s="1"/>
     </row>
-    <row r="408" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="5:6" ht="17.25" customHeight="1">
       <c r="E408" s="1"/>
       <c r="F408" s="1"/>
     </row>
-    <row r="409" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="5:6" ht="17.25" customHeight="1">
       <c r="E409" s="1"/>
       <c r="F409" s="1"/>
     </row>
-    <row r="410" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="5:6" ht="17.25" customHeight="1">
       <c r="E410" s="1"/>
       <c r="F410" s="1"/>
     </row>
-    <row r="411" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="5:6" ht="17.25" customHeight="1">
       <c r="E411" s="1"/>
       <c r="F411" s="1"/>
     </row>
-    <row r="412" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="5:6" ht="17.25" customHeight="1">
       <c r="E412" s="1"/>
       <c r="F412" s="1"/>
     </row>
-    <row r="413" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="5:6" ht="17.25" customHeight="1">
       <c r="E413" s="1"/>
       <c r="F413" s="1"/>
     </row>
-    <row r="414" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="5:6" ht="17.25" customHeight="1">
       <c r="E414" s="1"/>
       <c r="F414" s="1"/>
     </row>
-    <row r="415" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="5:6" ht="17.25" customHeight="1">
       <c r="E415" s="1"/>
       <c r="F415" s="1"/>
     </row>
-    <row r="416" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="5:6" ht="17.25" customHeight="1">
       <c r="E416" s="1"/>
       <c r="F416" s="1"/>
     </row>
-    <row r="417" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="5:6" ht="17.25" customHeight="1">
       <c r="E417" s="1"/>
       <c r="F417" s="1"/>
     </row>
-    <row r="418" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="5:6" ht="17.25" customHeight="1">
       <c r="E418" s="1"/>
       <c r="F418" s="1"/>
     </row>
-    <row r="419" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="5:6" ht="17.25" customHeight="1">
       <c r="E419" s="1"/>
       <c r="F419" s="1"/>
     </row>
-    <row r="420" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="5:6" ht="17.25" customHeight="1">
       <c r="E420" s="1"/>
       <c r="F420" s="1"/>
     </row>
-    <row r="421" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="5:6" ht="17.25" customHeight="1">
       <c r="E421" s="1"/>
       <c r="F421" s="1"/>
     </row>
-    <row r="422" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="5:6" ht="17.25" customHeight="1">
       <c r="E422" s="1"/>
       <c r="F422" s="1"/>
     </row>
-    <row r="423" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="5:6" ht="17.25" customHeight="1">
       <c r="E423" s="1"/>
       <c r="F423" s="1"/>
     </row>
-    <row r="424" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="5:6" ht="17.25" customHeight="1">
       <c r="E424" s="1"/>
       <c r="F424" s="1"/>
     </row>
-    <row r="425" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="5:6" ht="17.25" customHeight="1">
       <c r="E425" s="1"/>
       <c r="F425" s="1"/>
     </row>
-    <row r="426" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="5:6" ht="17.25" customHeight="1">
       <c r="E426" s="1"/>
       <c r="F426" s="1"/>
     </row>
-    <row r="427" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="5:6" ht="17.25" customHeight="1">
       <c r="E427" s="1"/>
       <c r="F427" s="1"/>
     </row>
-    <row r="428" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="5:6" ht="17.25" customHeight="1">
       <c r="E428" s="1"/>
       <c r="F428" s="1"/>
     </row>
-    <row r="429" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="5:6" ht="17.25" customHeight="1">
       <c r="E429" s="1"/>
       <c r="F429" s="1"/>
     </row>
-    <row r="430" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="5:6" ht="17.25" customHeight="1">
       <c r="E430" s="1"/>
       <c r="F430" s="1"/>
     </row>
-    <row r="431" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="5:6" ht="17.25" customHeight="1">
       <c r="E431" s="1"/>
       <c r="F431" s="1"/>
     </row>
-    <row r="432" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="5:6" ht="17.25" customHeight="1">
       <c r="E432" s="1"/>
       <c r="F432" s="1"/>
     </row>
-    <row r="433" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="5:6" ht="17.25" customHeight="1">
       <c r="E433" s="1"/>
       <c r="F433" s="1"/>
     </row>
-    <row r="434" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="5:6" ht="17.25" customHeight="1">
       <c r="E434" s="1"/>
       <c r="F434" s="1"/>
     </row>
-    <row r="435" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="5:6" ht="17.25" customHeight="1">
       <c r="E435" s="1"/>
       <c r="F435" s="1"/>
     </row>
-    <row r="436" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="5:6" ht="17.25" customHeight="1">
       <c r="E436" s="1"/>
       <c r="F436" s="1"/>
     </row>
-    <row r="437" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="5:6" ht="17.25" customHeight="1">
       <c r="E437" s="1"/>
       <c r="F437" s="1"/>
     </row>
-    <row r="438" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="5:6" ht="17.25" customHeight="1">
       <c r="E438" s="1"/>
       <c r="F438" s="1"/>
     </row>
-    <row r="439" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="5:6" ht="17.25" customHeight="1">
       <c r="E439" s="1"/>
       <c r="F439" s="1"/>
     </row>
-    <row r="440" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="5:6" ht="17.25" customHeight="1">
       <c r="E440" s="1"/>
       <c r="F440" s="1"/>
     </row>
-    <row r="441" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="5:6" ht="17.25" customHeight="1">
       <c r="E441" s="1"/>
       <c r="F441" s="1"/>
     </row>
-    <row r="442" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="5:6" ht="17.25" customHeight="1">
       <c r="E442" s="1"/>
       <c r="F442" s="1"/>
     </row>
-    <row r="443" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="5:6" ht="17.25" customHeight="1">
       <c r="E443" s="1"/>
       <c r="F443" s="1"/>
     </row>
-    <row r="444" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="5:6" ht="17.25" customHeight="1">
       <c r="E444" s="1"/>
       <c r="F444" s="1"/>
     </row>
-    <row r="445" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="5:6" ht="17.25" customHeight="1">
       <c r="E445" s="1"/>
       <c r="F445" s="1"/>
     </row>
-    <row r="446" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="5:6" ht="17.25" customHeight="1">
       <c r="E446" s="1"/>
       <c r="F446" s="1"/>
     </row>
-    <row r="447" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="5:6" ht="17.25" customHeight="1">
       <c r="E447" s="1"/>
       <c r="F447" s="1"/>
     </row>
-    <row r="448" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="5:6" ht="17.25" customHeight="1">
       <c r="E448" s="1"/>
       <c r="F448" s="1"/>
     </row>
-    <row r="449" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="5:6" ht="17.25" customHeight="1">
       <c r="E449" s="1"/>
       <c r="F449" s="1"/>
     </row>
-    <row r="450" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="5:6" ht="17.25" customHeight="1">
       <c r="E450" s="1"/>
       <c r="F450" s="1"/>
     </row>
-    <row r="451" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="5:6" ht="17.25" customHeight="1">
       <c r="E451" s="1"/>
       <c r="F451" s="1"/>
     </row>
-    <row r="452" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="5:6" ht="17.25" customHeight="1">
       <c r="E452" s="1"/>
       <c r="F452" s="1"/>
     </row>
-    <row r="453" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="5:6" ht="17.25" customHeight="1">
       <c r="E453" s="1"/>
       <c r="F453" s="1"/>
     </row>
-    <row r="454" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="5:6" ht="17.25" customHeight="1">
       <c r="E454" s="1"/>
       <c r="F454" s="1"/>
     </row>
-    <row r="455" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="5:6" ht="17.25" customHeight="1">
       <c r="E455" s="1"/>
       <c r="F455" s="1"/>
     </row>
-    <row r="456" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="5:6" ht="17.25" customHeight="1">
       <c r="E456" s="1"/>
       <c r="F456" s="1"/>
     </row>
-    <row r="457" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="5:6" ht="17.25" customHeight="1">
       <c r="E457" s="1"/>
       <c r="F457" s="1"/>
     </row>
-    <row r="458" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="5:6" ht="17.25" customHeight="1">
       <c r="E458" s="1"/>
       <c r="F458" s="1"/>
     </row>
-    <row r="459" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="5:6" ht="17.25" customHeight="1">
       <c r="E459" s="1"/>
       <c r="F459" s="1"/>
     </row>
-    <row r="460" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="5:6" ht="17.25" customHeight="1">
       <c r="E460" s="1"/>
       <c r="F460" s="1"/>
     </row>
-    <row r="461" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="5:6" ht="17.25" customHeight="1">
       <c r="E461" s="1"/>
       <c r="F461" s="1"/>
     </row>
-    <row r="462" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="5:6" ht="17.25" customHeight="1">
       <c r="E462" s="1"/>
       <c r="F462" s="1"/>
     </row>
-    <row r="463" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="5:6" ht="17.25" customHeight="1">
       <c r="E463" s="1"/>
       <c r="F463" s="1"/>
     </row>
-    <row r="464" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="5:6" ht="17.25" customHeight="1">
       <c r="E464" s="1"/>
       <c r="F464" s="1"/>
     </row>
-    <row r="465" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="5:6" ht="17.25" customHeight="1">
       <c r="E465" s="1"/>
       <c r="F465" s="1"/>
     </row>
-    <row r="466" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="5:6" ht="17.25" customHeight="1">
       <c r="E466" s="1"/>
       <c r="F466" s="1"/>
     </row>
-    <row r="467" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="5:6" ht="17.25" customHeight="1">
       <c r="E467" s="1"/>
       <c r="F467" s="1"/>
     </row>
-    <row r="468" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="5:6" ht="17.25" customHeight="1">
       <c r="E468" s="1"/>
       <c r="F468" s="1"/>
     </row>
-    <row r="469" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="5:6" ht="17.25" customHeight="1">
       <c r="E469" s="1"/>
       <c r="F469" s="1"/>
     </row>
-    <row r="470" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="5:6" ht="17.25" customHeight="1">
       <c r="E470" s="1"/>
       <c r="F470" s="1"/>
     </row>
-    <row r="471" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="5:6" ht="17.25" customHeight="1">
       <c r="E471" s="1"/>
       <c r="F471" s="1"/>
     </row>
-    <row r="472" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="5:6" ht="17.25" customHeight="1">
       <c r="E472" s="1"/>
       <c r="F472" s="1"/>
     </row>
-    <row r="473" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="5:6" ht="17.25" customHeight="1">
       <c r="E473" s="1"/>
       <c r="F473" s="1"/>
     </row>
-    <row r="474" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="5:6" ht="17.25" customHeight="1">
       <c r="E474" s="1"/>
       <c r="F474" s="1"/>
     </row>
-    <row r="475" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="5:6" ht="17.25" customHeight="1">
       <c r="E475" s="1"/>
       <c r="F475" s="1"/>
     </row>
-    <row r="476" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="5:6" ht="17.25" customHeight="1">
       <c r="E476" s="1"/>
       <c r="F476" s="1"/>
     </row>
-    <row r="477" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="5:6" ht="17.25" customHeight="1">
       <c r="E477" s="1"/>
       <c r="F477" s="1"/>
     </row>
-    <row r="478" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="5:6" ht="17.25" customHeight="1">
       <c r="E478" s="1"/>
       <c r="F478" s="1"/>
     </row>
-    <row r="479" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="5:6" ht="17.25" customHeight="1">
       <c r="E479" s="1"/>
       <c r="F479" s="1"/>
     </row>
-    <row r="480" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="5:6" ht="17.25" customHeight="1">
       <c r="E480" s="1"/>
       <c r="F480" s="1"/>
     </row>
-    <row r="481" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="5:6" ht="17.25" customHeight="1">
       <c r="E481" s="1"/>
       <c r="F481" s="1"/>
     </row>
-    <row r="482" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="5:6" ht="17.25" customHeight="1">
       <c r="E482" s="1"/>
       <c r="F482" s="1"/>
     </row>
-    <row r="483" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="5:6" ht="17.25" customHeight="1">
       <c r="E483" s="1"/>
       <c r="F483" s="1"/>
     </row>
-    <row r="484" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="5:6" ht="17.25" customHeight="1">
       <c r="E484" s="1"/>
       <c r="F484" s="1"/>
     </row>
-    <row r="485" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="5:6" ht="17.25" customHeight="1">
       <c r="E485" s="1"/>
       <c r="F485" s="1"/>
     </row>
-    <row r="486" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="5:6" ht="17.25" customHeight="1">
       <c r="E486" s="1"/>
       <c r="F486" s="1"/>
     </row>
-    <row r="487" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="5:6" ht="17.25" customHeight="1">
       <c r="E487" s="1"/>
       <c r="F487" s="1"/>
     </row>
-    <row r="488" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="5:6" ht="17.25" customHeight="1">
       <c r="E488" s="1"/>
       <c r="F488" s="1"/>
     </row>
-    <row r="489" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="5:6" ht="17.25" customHeight="1">
       <c r="E489" s="1"/>
       <c r="F489" s="1"/>
     </row>
-    <row r="490" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="5:6" ht="17.25" customHeight="1">
       <c r="E490" s="1"/>
       <c r="F490" s="1"/>
     </row>
-    <row r="491" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="5:6" ht="17.25" customHeight="1">
       <c r="E491" s="1"/>
       <c r="F491" s="1"/>
     </row>
-    <row r="492" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="5:6" ht="17.25" customHeight="1">
       <c r="E492" s="1"/>
       <c r="F492" s="1"/>
     </row>
-    <row r="493" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="5:6" ht="17.25" customHeight="1">
       <c r="E493" s="1"/>
       <c r="F493" s="1"/>
     </row>
-    <row r="494" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="5:6" ht="17.25" customHeight="1">
       <c r="E494" s="1"/>
       <c r="F494" s="1"/>
     </row>
-    <row r="495" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="5:6" ht="17.25" customHeight="1">
       <c r="E495" s="1"/>
       <c r="F495" s="1"/>
     </row>
-    <row r="496" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="5:6" ht="17.25" customHeight="1">
       <c r="E496" s="1"/>
       <c r="F496" s="1"/>
     </row>
-    <row r="497" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="5:6" ht="17.25" customHeight="1">
       <c r="E497" s="1"/>
       <c r="F497" s="1"/>
     </row>
-    <row r="498" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="5:6" ht="17.25" customHeight="1">
       <c r="E498" s="1"/>
       <c r="F498" s="1"/>
     </row>
-    <row r="499" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="5:6" ht="17.25" customHeight="1">
       <c r="E499" s="1"/>
       <c r="F499" s="1"/>
     </row>
-    <row r="500" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="5:6" ht="17.25" customHeight="1">
       <c r="E500" s="1"/>
       <c r="F500" s="1"/>
     </row>
-    <row r="501" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="5:6" ht="17.25" customHeight="1">
       <c r="E501" s="1"/>
       <c r="F501" s="1"/>
     </row>
-    <row r="502" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="5:6" ht="17.25" customHeight="1">
       <c r="E502" s="1"/>
       <c r="F502" s="1"/>
     </row>
-    <row r="503" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="5:6" ht="17.25" customHeight="1">
       <c r="E503" s="1"/>
       <c r="F503" s="1"/>
     </row>
-    <row r="504" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="5:6" ht="17.25" customHeight="1">
       <c r="E504" s="1"/>
       <c r="F504" s="1"/>
     </row>
-    <row r="505" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="5:6" ht="17.25" customHeight="1">
       <c r="E505" s="1"/>
       <c r="F505" s="1"/>
     </row>
-    <row r="506" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="5:6" ht="17.25" customHeight="1">
       <c r="E506" s="1"/>
       <c r="F506" s="1"/>
     </row>
-    <row r="507" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="5:6" ht="17.25" customHeight="1">
       <c r="E507" s="1"/>
       <c r="F507" s="1"/>
     </row>
-    <row r="508" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="5:6" ht="17.25" customHeight="1">
       <c r="E508" s="1"/>
       <c r="F508" s="1"/>
     </row>
-    <row r="509" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="5:6" ht="17.25" customHeight="1">
       <c r="E509" s="1"/>
       <c r="F509" s="1"/>
     </row>
-    <row r="510" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="5:6" ht="17.25" customHeight="1">
       <c r="E510" s="1"/>
       <c r="F510" s="1"/>
     </row>
-    <row r="511" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="5:6" ht="17.25" customHeight="1">
       <c r="E511" s="1"/>
       <c r="F511" s="1"/>
     </row>
-    <row r="512" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="5:6" ht="17.25" customHeight="1">
       <c r="E512" s="1"/>
       <c r="F512" s="1"/>
     </row>
-    <row r="513" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="5:6" ht="17.25" customHeight="1">
       <c r="E513" s="1"/>
       <c r="F513" s="1"/>
     </row>
-    <row r="514" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="5:6" ht="17.25" customHeight="1">
       <c r="E514" s="1"/>
       <c r="F514" s="1"/>
     </row>
-    <row r="515" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="5:6" ht="17.25" customHeight="1">
       <c r="E515" s="1"/>
       <c r="F515" s="1"/>
     </row>
-    <row r="516" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="5:6" ht="17.25" customHeight="1">
       <c r="E516" s="1"/>
       <c r="F516" s="1"/>
     </row>
-    <row r="517" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="5:6" ht="17.25" customHeight="1">
       <c r="E517" s="1"/>
       <c r="F517" s="1"/>
     </row>
-    <row r="518" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="5:6" ht="17.25" customHeight="1">
       <c r="E518" s="1"/>
       <c r="F518" s="1"/>
     </row>
-    <row r="519" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="5:6" ht="17.25" customHeight="1">
       <c r="E519" s="1"/>
       <c r="F519" s="1"/>
     </row>
-    <row r="520" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="5:6" ht="17.25" customHeight="1">
       <c r="E520" s="1"/>
       <c r="F520" s="1"/>
     </row>
-    <row r="521" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="5:6" ht="17.25" customHeight="1">
       <c r="E521" s="1"/>
       <c r="F521" s="1"/>
     </row>
-    <row r="522" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="5:6" ht="17.25" customHeight="1">
       <c r="E522" s="1"/>
       <c r="F522" s="1"/>
     </row>
-    <row r="523" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="5:6" ht="17.25" customHeight="1">
       <c r="E523" s="1"/>
       <c r="F523" s="1"/>
     </row>
-    <row r="524" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="5:6" ht="17.25" customHeight="1">
       <c r="E524" s="1"/>
       <c r="F524" s="1"/>
     </row>
-    <row r="525" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="5:6" ht="17.25" customHeight="1">
       <c r="E525" s="1"/>
       <c r="F525" s="1"/>
     </row>
-    <row r="526" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="5:6" ht="17.25" customHeight="1">
       <c r="E526" s="1"/>
       <c r="F526" s="1"/>
     </row>
-    <row r="527" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="5:6" ht="17.25" customHeight="1">
       <c r="E527" s="1"/>
       <c r="F527" s="1"/>
     </row>
-    <row r="528" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="5:6" ht="17.25" customHeight="1">
       <c r="E528" s="1"/>
       <c r="F528" s="1"/>
     </row>
-    <row r="529" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="5:6" ht="17.25" customHeight="1">
       <c r="E529" s="1"/>
       <c r="F529" s="1"/>
     </row>
-    <row r="530" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="5:6" ht="17.25" customHeight="1">
       <c r="E530" s="1"/>
       <c r="F530" s="1"/>
     </row>
-    <row r="531" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="5:6" ht="17.25" customHeight="1">
       <c r="E531" s="1"/>
       <c r="F531" s="1"/>
     </row>
-    <row r="532" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="5:6" ht="17.25" customHeight="1">
       <c r="E532" s="1"/>
       <c r="F532" s="1"/>
     </row>
-    <row r="533" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="5:6" ht="17.25" customHeight="1">
       <c r="E533" s="1"/>
       <c r="F533" s="1"/>
     </row>
-    <row r="534" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="5:6" ht="17.25" customHeight="1">
       <c r="E534" s="1"/>
       <c r="F534" s="1"/>
     </row>
-    <row r="535" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="5:6" ht="17.25" customHeight="1">
       <c r="E535" s="1"/>
       <c r="F535" s="1"/>
     </row>
-    <row r="536" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="5:6" ht="17.25" customHeight="1">
       <c r="E536" s="1"/>
       <c r="F536" s="1"/>
     </row>
-    <row r="537" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="5:6" ht="17.25" customHeight="1">
       <c r="E537" s="1"/>
       <c r="F537" s="1"/>
     </row>
-    <row r="538" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="5:6" ht="17.25" customHeight="1">
       <c r="E538" s="1"/>
       <c r="F538" s="1"/>
     </row>
-    <row r="539" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="5:6" ht="17.25" customHeight="1">
       <c r="E539" s="1"/>
       <c r="F539" s="1"/>
     </row>
-    <row r="540" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="5:6" ht="17.25" customHeight="1">
       <c r="E540" s="1"/>
       <c r="F540" s="1"/>
     </row>
-    <row r="541" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="5:6" ht="17.25" customHeight="1">
       <c r="E541" s="1"/>
       <c r="F541" s="1"/>
     </row>
-    <row r="542" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="5:6" ht="17.25" customHeight="1">
       <c r="E542" s="1"/>
       <c r="F542" s="1"/>
     </row>
-    <row r="543" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="5:6" ht="17.25" customHeight="1">
       <c r="E543" s="1"/>
       <c r="F543" s="1"/>
     </row>
-    <row r="544" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="5:6" ht="17.25" customHeight="1">
       <c r="E544" s="1"/>
       <c r="F544" s="1"/>
     </row>
-    <row r="545" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="5:6" ht="17.25" customHeight="1">
       <c r="E545" s="1"/>
       <c r="F545" s="1"/>
     </row>
-    <row r="546" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="5:6" ht="17.25" customHeight="1">
       <c r="E546" s="1"/>
       <c r="F546" s="1"/>
     </row>
-    <row r="547" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="5:6" ht="17.25" customHeight="1">
       <c r="E547" s="1"/>
       <c r="F547" s="1"/>
     </row>
-    <row r="548" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="5:6" ht="17.25" customHeight="1">
       <c r="E548" s="1"/>
       <c r="F548" s="1"/>
     </row>
-    <row r="549" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="5:6" ht="17.25" customHeight="1">
       <c r="E549" s="1"/>
       <c r="F549" s="1"/>
     </row>
-    <row r="550" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="5:6" ht="17.25" customHeight="1">
       <c r="E550" s="1"/>
       <c r="F550" s="1"/>
     </row>
-    <row r="551" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="5:6" ht="17.25" customHeight="1">
       <c r="E551" s="1"/>
       <c r="F551" s="1"/>
     </row>
-    <row r="552" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="5:6" ht="17.25" customHeight="1">
       <c r="E552" s="1"/>
       <c r="F552" s="1"/>
     </row>
-    <row r="553" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="5:6" ht="17.25" customHeight="1">
       <c r="E553" s="1"/>
       <c r="F553" s="1"/>
     </row>
-    <row r="554" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="5:6" ht="17.25" customHeight="1">
       <c r="E554" s="1"/>
       <c r="F554" s="1"/>
     </row>
-    <row r="555" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="5:6" ht="17.25" customHeight="1">
       <c r="E555" s="1"/>
       <c r="F555" s="1"/>
     </row>
-    <row r="556" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="5:6" ht="17.25" customHeight="1">
       <c r="E556" s="1"/>
       <c r="F556" s="1"/>
     </row>
-    <row r="557" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="5:6" ht="17.25" customHeight="1">
       <c r="E557" s="1"/>
       <c r="F557" s="1"/>
     </row>
-    <row r="558" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="5:6" ht="17.25" customHeight="1">
       <c r="E558" s="1"/>
       <c r="F558" s="1"/>
     </row>
-    <row r="559" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="5:6" ht="17.25" customHeight="1">
       <c r="E559" s="1"/>
       <c r="F559" s="1"/>
     </row>
-    <row r="560" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="5:6" ht="17.25" customHeight="1">
       <c r="E560" s="1"/>
       <c r="F560" s="1"/>
     </row>
-    <row r="561" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="5:6" ht="17.25" customHeight="1">
       <c r="E561" s="1"/>
       <c r="F561" s="1"/>
     </row>
-    <row r="562" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="5:6" ht="17.25" customHeight="1">
       <c r="E562" s="1"/>
       <c r="F562" s="1"/>
     </row>
-    <row r="563" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="5:6" ht="17.25" customHeight="1">
       <c r="E563" s="1"/>
       <c r="F563" s="1"/>
     </row>
-    <row r="564" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="5:6" ht="17.25" customHeight="1">
       <c r="E564" s="1"/>
       <c r="F564" s="1"/>
     </row>
-    <row r="565" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="5:6" ht="17.25" customHeight="1">
       <c r="E565" s="1"/>
       <c r="F565" s="1"/>
     </row>
-    <row r="566" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="5:6" ht="17.25" customHeight="1">
       <c r="E566" s="1"/>
       <c r="F566" s="1"/>
     </row>
-    <row r="567" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="5:6" ht="17.25" customHeight="1">
       <c r="E567" s="1"/>
       <c r="F567" s="1"/>
     </row>
-    <row r="568" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="5:6" ht="17.25" customHeight="1">
       <c r="E568" s="1"/>
       <c r="F568" s="1"/>
     </row>
-    <row r="569" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="5:6" ht="17.25" customHeight="1">
       <c r="E569" s="1"/>
       <c r="F569" s="1"/>
     </row>
-    <row r="570" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="5:6" ht="17.25" customHeight="1">
       <c r="E570" s="1"/>
       <c r="F570" s="1"/>
     </row>
-    <row r="571" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="5:6" ht="17.25" customHeight="1">
       <c r="E571" s="1"/>
       <c r="F571" s="1"/>
     </row>
-    <row r="572" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="5:6" ht="17.25" customHeight="1">
       <c r="E572" s="1"/>
       <c r="F572" s="1"/>
     </row>
-    <row r="573" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="5:6" ht="17.25" customHeight="1">
       <c r="E573" s="1"/>
       <c r="F573" s="1"/>
     </row>
-    <row r="574" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="5:6" ht="17.25" customHeight="1">
       <c r="E574" s="1"/>
       <c r="F574" s="1"/>
     </row>
-    <row r="575" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="5:6" ht="17.25" customHeight="1">
       <c r="E575" s="1"/>
       <c r="F575" s="1"/>
     </row>
-    <row r="576" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="5:6" ht="17.25" customHeight="1">
       <c r="E576" s="1"/>
       <c r="F576" s="1"/>
     </row>
-    <row r="577" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="5:6" ht="17.25" customHeight="1">
       <c r="E577" s="1"/>
       <c r="F577" s="1"/>
     </row>
-    <row r="578" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="5:6" ht="17.25" customHeight="1">
       <c r="E578" s="1"/>
       <c r="F578" s="1"/>
     </row>
-    <row r="579" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="5:6" ht="17.25" customHeight="1">
       <c r="E579" s="1"/>
       <c r="F579" s="1"/>
     </row>
-    <row r="580" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="5:6" ht="17.25" customHeight="1">
       <c r="E580" s="1"/>
       <c r="F580" s="1"/>
     </row>
-    <row r="581" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="5:6" ht="17.25" customHeight="1">
       <c r="E581" s="1"/>
       <c r="F581" s="1"/>
     </row>
-    <row r="582" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="5:6" ht="17.25" customHeight="1">
       <c r="E582" s="1"/>
       <c r="F582" s="1"/>
     </row>
-    <row r="583" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="5:6" ht="17.25" customHeight="1">
       <c r="E583" s="1"/>
       <c r="F583" s="1"/>
     </row>
-    <row r="584" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="5:6" ht="17.25" customHeight="1">
       <c r="E584" s="1"/>
       <c r="F584" s="1"/>
     </row>
-    <row r="585" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="5:6" ht="17.25" customHeight="1">
       <c r="E585" s="1"/>
       <c r="F585" s="1"/>
     </row>
-    <row r="586" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="5:6" ht="17.25" customHeight="1">
       <c r="E586" s="1"/>
       <c r="F586" s="1"/>
     </row>
-    <row r="587" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="5:6" ht="17.25" customHeight="1">
       <c r="E587" s="1"/>
       <c r="F587" s="1"/>
     </row>
-    <row r="588" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="5:6" ht="17.25" customHeight="1">
       <c r="E588" s="1"/>
       <c r="F588" s="1"/>
     </row>
-    <row r="589" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="5:6" ht="17.25" customHeight="1">
       <c r="E589" s="1"/>
       <c r="F589" s="1"/>
     </row>
-    <row r="590" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="5:6" ht="17.25" customHeight="1">
       <c r="E590" s="1"/>
       <c r="F590" s="1"/>
     </row>
-    <row r="591" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="5:6" ht="17.25" customHeight="1">
       <c r="E591" s="1"/>
       <c r="F591" s="1"/>
     </row>
-    <row r="592" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="5:6" ht="17.25" customHeight="1">
       <c r="E592" s="1"/>
       <c r="F592" s="1"/>
     </row>
-    <row r="593" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="5:6" ht="17.25" customHeight="1">
       <c r="E593" s="1"/>
       <c r="F593" s="1"/>
     </row>
-    <row r="594" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="5:6" ht="17.25" customHeight="1">
       <c r="E594" s="1"/>
       <c r="F594" s="1"/>
     </row>
-    <row r="595" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="5:6" ht="17.25" customHeight="1">
       <c r="E595" s="1"/>
       <c r="F595" s="1"/>
     </row>
-    <row r="596" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="5:6" ht="17.25" customHeight="1">
       <c r="E596" s="1"/>
       <c r="F596" s="1"/>
     </row>
-    <row r="597" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="5:6" ht="17.25" customHeight="1">
       <c r="E597" s="1"/>
       <c r="F597" s="1"/>
     </row>
-    <row r="598" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="5:6" ht="17.25" customHeight="1">
       <c r="E598" s="1"/>
       <c r="F598" s="1"/>
     </row>
-    <row r="599" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="5:6" ht="17.25" customHeight="1">
       <c r="E599" s="1"/>
       <c r="F599" s="1"/>
     </row>
-    <row r="600" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="5:6" ht="17.25" customHeight="1">
       <c r="E600" s="1"/>
       <c r="F600" s="1"/>
     </row>
-    <row r="601" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="5:6" ht="17.25" customHeight="1">
       <c r="E601" s="1"/>
       <c r="F601" s="1"/>
     </row>
-    <row r="602" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="5:6" ht="17.25" customHeight="1">
       <c r="E602" s="1"/>
       <c r="F602" s="1"/>
     </row>
-    <row r="603" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="5:6" ht="17.25" customHeight="1">
       <c r="E603" s="1"/>
       <c r="F603" s="1"/>
     </row>
-    <row r="604" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="5:6" ht="17.25" customHeight="1">
       <c r="E604" s="1"/>
       <c r="F604" s="1"/>
     </row>
-    <row r="605" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="5:6" ht="17.25" customHeight="1">
       <c r="E605" s="1"/>
       <c r="F605" s="1"/>
     </row>
-    <row r="606" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="5:6" ht="17.25" customHeight="1">
       <c r="E606" s="1"/>
       <c r="F606" s="1"/>
     </row>
-    <row r="607" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="5:6" ht="17.25" customHeight="1">
       <c r="E607" s="1"/>
       <c r="F607" s="1"/>
     </row>
-    <row r="608" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="5:6" ht="17.25" customHeight="1">
       <c r="E608" s="1"/>
       <c r="F608" s="1"/>
     </row>
-    <row r="609" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="5:6" ht="17.25" customHeight="1">
       <c r="E609" s="1"/>
       <c r="F609" s="1"/>
     </row>
-    <row r="610" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="5:6" ht="17.25" customHeight="1">
       <c r="E610" s="1"/>
       <c r="F610" s="1"/>
     </row>
-    <row r="611" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="5:6" ht="17.25" customHeight="1">
       <c r="E611" s="1"/>
       <c r="F611" s="1"/>
     </row>
-    <row r="612" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="5:6" ht="17.25" customHeight="1">
       <c r="E612" s="1"/>
       <c r="F612" s="1"/>
     </row>
-    <row r="613" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="5:6" ht="17.25" customHeight="1">
       <c r="E613" s="1"/>
       <c r="F613" s="1"/>
     </row>
-    <row r="614" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="5:6" ht="17.25" customHeight="1">
       <c r="E614" s="1"/>
       <c r="F614" s="1"/>
     </row>
-    <row r="615" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="5:6" ht="17.25" customHeight="1">
       <c r="E615" s="1"/>
       <c r="F615" s="1"/>
     </row>
-    <row r="616" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="5:6" ht="17.25" customHeight="1">
       <c r="E616" s="1"/>
       <c r="F616" s="1"/>
     </row>
-    <row r="617" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="5:6" ht="17.25" customHeight="1">
       <c r="E617" s="1"/>
       <c r="F617" s="1"/>
     </row>
-    <row r="618" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="5:6" ht="17.25" customHeight="1">
       <c r="E618" s="1"/>
       <c r="F618" s="1"/>
     </row>
-    <row r="619" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="5:6" ht="17.25" customHeight="1">
       <c r="E619" s="1"/>
       <c r="F619" s="1"/>
     </row>
-    <row r="620" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="5:6" ht="17.25" customHeight="1">
       <c r="E620" s="1"/>
       <c r="F620" s="1"/>
     </row>
-    <row r="621" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="5:6" ht="17.25" customHeight="1">
       <c r="E621" s="1"/>
       <c r="F621" s="1"/>
     </row>
-    <row r="622" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="5:6" ht="17.25" customHeight="1">
       <c r="E622" s="1"/>
       <c r="F622" s="1"/>
     </row>
-    <row r="623" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="5:6" ht="17.25" customHeight="1">
       <c r="E623" s="1"/>
       <c r="F623" s="1"/>
     </row>
-    <row r="624" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="5:6" ht="17.25" customHeight="1">
       <c r="E624" s="1"/>
       <c r="F624" s="1"/>
     </row>
-    <row r="625" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="5:6" ht="17.25" customHeight="1">
       <c r="E625" s="1"/>
       <c r="F625" s="1"/>
     </row>
-    <row r="626" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="5:6" ht="17.25" customHeight="1">
       <c r="E626" s="1"/>
       <c r="F626" s="1"/>
     </row>
-    <row r="627" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="5:6" ht="17.25" customHeight="1">
       <c r="E627" s="1"/>
       <c r="F627" s="1"/>
     </row>
-    <row r="628" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="5:6" ht="17.25" customHeight="1">
       <c r="E628" s="1"/>
       <c r="F628" s="1"/>
     </row>
-    <row r="629" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="5:6" ht="17.25" customHeight="1">
       <c r="E629" s="1"/>
       <c r="F629" s="1"/>
     </row>
-    <row r="630" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="5:6" ht="17.25" customHeight="1">
       <c r="E630" s="1"/>
       <c r="F630" s="1"/>
     </row>
-    <row r="631" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="5:6" ht="17.25" customHeight="1">
       <c r="E631" s="1"/>
       <c r="F631" s="1"/>
     </row>
-    <row r="632" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="5:6" ht="17.25" customHeight="1">
       <c r="E632" s="1"/>
       <c r="F632" s="1"/>
     </row>
-    <row r="633" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="5:6" ht="17.25" customHeight="1">
       <c r="E633" s="1"/>
       <c r="F633" s="1"/>
     </row>
-    <row r="634" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="5:6" ht="17.25" customHeight="1">
       <c r="E634" s="1"/>
       <c r="F634" s="1"/>
     </row>
-    <row r="635" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="5:6" ht="17.25" customHeight="1">
       <c r="E635" s="1"/>
       <c r="F635" s="1"/>
     </row>
-    <row r="636" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="5:6" ht="17.25" customHeight="1">
       <c r="E636" s="1"/>
       <c r="F636" s="1"/>
     </row>
-    <row r="637" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="5:6" ht="17.25" customHeight="1">
       <c r="E637" s="1"/>
       <c r="F637" s="1"/>
     </row>
-    <row r="638" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="5:6" ht="17.25" customHeight="1">
       <c r="E638" s="1"/>
       <c r="F638" s="1"/>
     </row>
-    <row r="639" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="5:6" ht="17.25" customHeight="1">
       <c r="E639" s="1"/>
       <c r="F639" s="1"/>
     </row>
-    <row r="640" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="5:6" ht="17.25" customHeight="1">
       <c r="E640" s="1"/>
       <c r="F640" s="1"/>
     </row>
-    <row r="641" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="5:6" ht="17.25" customHeight="1">
       <c r="E641" s="1"/>
       <c r="F641" s="1"/>
     </row>
-    <row r="642" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="5:6" ht="17.25" customHeight="1">
       <c r="E642" s="1"/>
       <c r="F642" s="1"/>
     </row>
-    <row r="643" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="5:6" ht="17.25" customHeight="1">
       <c r="E643" s="1"/>
       <c r="F643" s="1"/>
     </row>
-    <row r="644" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="5:6" ht="17.25" customHeight="1">
       <c r="E644" s="1"/>
       <c r="F644" s="1"/>
     </row>
-    <row r="645" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="5:6" ht="17.25" customHeight="1">
       <c r="E645" s="1"/>
       <c r="F645" s="1"/>
     </row>
-    <row r="646" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="5:6" ht="17.25" customHeight="1">
       <c r="E646" s="1"/>
       <c r="F646" s="1"/>
     </row>
-    <row r="647" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="5:6" ht="17.25" customHeight="1">
       <c r="E647" s="1"/>
       <c r="F647" s="1"/>
     </row>
-    <row r="648" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="5:6" ht="17.25" customHeight="1">
       <c r="E648" s="1"/>
       <c r="F648" s="1"/>
     </row>
-    <row r="649" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="5:6" ht="17.25" customHeight="1">
       <c r="E649" s="1"/>
       <c r="F649" s="1"/>
     </row>
-    <row r="650" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="5:6" ht="17.25" customHeight="1">
       <c r="E650" s="1"/>
       <c r="F650" s="1"/>
     </row>
-    <row r="651" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="5:6" ht="17.25" customHeight="1">
       <c r="E651" s="1"/>
       <c r="F651" s="1"/>
     </row>
-    <row r="652" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="5:6" ht="17.25" customHeight="1">
       <c r="E652" s="1"/>
       <c r="F652" s="1"/>
     </row>
-    <row r="653" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="5:6" ht="17.25" customHeight="1">
       <c r="E653" s="1"/>
       <c r="F653" s="1"/>
     </row>
-    <row r="654" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="5:6" ht="17.25" customHeight="1">
       <c r="E654" s="1"/>
       <c r="F654" s="1"/>
     </row>
-    <row r="655" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="5:6" ht="17.25" customHeight="1">
       <c r="E655" s="1"/>
       <c r="F655" s="1"/>
     </row>
-    <row r="656" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="5:6" ht="17.25" customHeight="1">
       <c r="E656" s="1"/>
       <c r="F656" s="1"/>
     </row>
-    <row r="657" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="5:6" ht="17.25" customHeight="1">
       <c r="E657" s="1"/>
       <c r="F657" s="1"/>
     </row>
-    <row r="658" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="5:6" ht="17.25" customHeight="1">
       <c r="E658" s="1"/>
       <c r="F658" s="1"/>
     </row>
-    <row r="659" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="5:6" ht="17.25" customHeight="1">
       <c r="E659" s="1"/>
       <c r="F659" s="1"/>
     </row>
-    <row r="660" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="5:6" ht="17.25" customHeight="1">
       <c r="E660" s="1"/>
       <c r="F660" s="1"/>
     </row>
-    <row r="661" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="5:6" ht="17.25" customHeight="1">
       <c r="E661" s="1"/>
       <c r="F661" s="1"/>
     </row>
-    <row r="662" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="5:6" ht="17.25" customHeight="1">
       <c r="E662" s="1"/>
       <c r="F662" s="1"/>
     </row>
-    <row r="663" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="5:6" ht="17.25" customHeight="1">
       <c r="E663" s="1"/>
       <c r="F663" s="1"/>
     </row>
-    <row r="664" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="5:6" ht="17.25" customHeight="1">
       <c r="E664" s="1"/>
       <c r="F664" s="1"/>
     </row>
-    <row r="665" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="5:6" ht="17.25" customHeight="1">
       <c r="E665" s="1"/>
       <c r="F665" s="1"/>
     </row>
-    <row r="666" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="5:6" ht="17.25" customHeight="1">
       <c r="E666" s="1"/>
       <c r="F666" s="1"/>
     </row>
-    <row r="667" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="5:6" ht="17.25" customHeight="1">
       <c r="E667" s="1"/>
       <c r="F667" s="1"/>
     </row>
-    <row r="668" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="5:6" ht="17.25" customHeight="1">
       <c r="E668" s="1"/>
       <c r="F668" s="1"/>
     </row>
-    <row r="669" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="5:6" ht="17.25" customHeight="1">
       <c r="E669" s="1"/>
       <c r="F669" s="1"/>
     </row>
-    <row r="670" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="5:6" ht="17.25" customHeight="1">
       <c r="E670" s="1"/>
       <c r="F670" s="1"/>
     </row>
-    <row r="671" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="5:6" ht="17.25" customHeight="1">
       <c r="E671" s="1"/>
       <c r="F671" s="1"/>
     </row>
-    <row r="672" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="5:6" ht="17.25" customHeight="1">
       <c r="E672" s="1"/>
       <c r="F672" s="1"/>
     </row>
-    <row r="673" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="5:6" ht="17.25" customHeight="1">
       <c r="E673" s="1"/>
       <c r="F673" s="1"/>
     </row>
-    <row r="674" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="5:6" ht="17.25" customHeight="1">
       <c r="E674" s="1"/>
       <c r="F674" s="1"/>
     </row>
-    <row r="675" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="5:6" ht="17.25" customHeight="1">
       <c r="E675" s="1"/>
       <c r="F675" s="1"/>
     </row>
-    <row r="676" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="5:6" ht="17.25" customHeight="1">
       <c r="E676" s="1"/>
       <c r="F676" s="1"/>
     </row>
-    <row r="677" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="5:6" ht="17.25" customHeight="1">
       <c r="E677" s="1"/>
       <c r="F677" s="1"/>
     </row>
-    <row r="678" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="5:6" ht="17.25" customHeight="1">
       <c r="E678" s="1"/>
       <c r="F678" s="1"/>
     </row>
-    <row r="679" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="5:6" ht="17.25" customHeight="1">
       <c r="E679" s="1"/>
       <c r="F679" s="1"/>
     </row>
-    <row r="680" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="5:6" ht="17.25" customHeight="1">
       <c r="E680" s="1"/>
       <c r="F680" s="1"/>
     </row>
-    <row r="681" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="5:6" ht="17.25" customHeight="1">
       <c r="E681" s="1"/>
       <c r="F681" s="1"/>
     </row>
-    <row r="682" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="5:6" ht="17.25" customHeight="1">
       <c r="E682" s="1"/>
       <c r="F682" s="1"/>
     </row>
-    <row r="683" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="5:6" ht="17.25" customHeight="1">
       <c r="E683" s="1"/>
       <c r="F683" s="1"/>
     </row>
-    <row r="684" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="5:6" ht="17.25" customHeight="1">
       <c r="E684" s="1"/>
       <c r="F684" s="1"/>
     </row>
-    <row r="685" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="5:6" ht="17.25" customHeight="1">
       <c r="E685" s="1"/>
       <c r="F685" s="1"/>
     </row>
-    <row r="686" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="5:6" ht="17.25" customHeight="1">
       <c r="E686" s="1"/>
       <c r="F686" s="1"/>
     </row>
-    <row r="687" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="5:6" ht="17.25" customHeight="1">
       <c r="E687" s="1"/>
       <c r="F687" s="1"/>
     </row>
-    <row r="688" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="5:6" ht="17.25" customHeight="1">
       <c r="E688" s="1"/>
       <c r="F688" s="1"/>
     </row>
-    <row r="689" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="5:6" ht="17.25" customHeight="1">
       <c r="E689" s="1"/>
       <c r="F689" s="1"/>
     </row>
-    <row r="690" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="5:6" ht="17.25" customHeight="1">
       <c r="E690" s="1"/>
       <c r="F690" s="1"/>
     </row>
-    <row r="691" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="5:6" ht="17.25" customHeight="1">
       <c r="E691" s="1"/>
       <c r="F691" s="1"/>
     </row>
-    <row r="692" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="5:6" ht="17.25" customHeight="1">
       <c r="E692" s="1"/>
       <c r="F692" s="1"/>
     </row>
-    <row r="693" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="5:6" ht="17.25" customHeight="1">
       <c r="E693" s="1"/>
       <c r="F693" s="1"/>
     </row>
-    <row r="694" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="5:6" ht="17.25" customHeight="1">
       <c r="E694" s="1"/>
       <c r="F694" s="1"/>
     </row>
-    <row r="695" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="5:6" ht="17.25" customHeight="1">
       <c r="E695" s="1"/>
       <c r="F695" s="1"/>
     </row>
-    <row r="696" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="5:6" ht="17.25" customHeight="1">
       <c r="E696" s="1"/>
       <c r="F696" s="1"/>
     </row>
-    <row r="697" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="5:6" ht="17.25" customHeight="1">
       <c r="E697" s="1"/>
       <c r="F697" s="1"/>
     </row>
-    <row r="698" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="5:6" ht="17.25" customHeight="1">
       <c r="E698" s="1"/>
       <c r="F698" s="1"/>
     </row>
-    <row r="699" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="5:6" ht="17.25" customHeight="1">
       <c r="E699" s="1"/>
       <c r="F699" s="1"/>
     </row>
-    <row r="700" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="5:6" ht="17.25" customHeight="1">
       <c r="E700" s="1"/>
       <c r="F700" s="1"/>
     </row>
-    <row r="701" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="5:6" ht="17.25" customHeight="1">
       <c r="E701" s="1"/>
       <c r="F701" s="1"/>
     </row>
-    <row r="702" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="5:6" ht="17.25" customHeight="1">
       <c r="E702" s="1"/>
       <c r="F702" s="1"/>
     </row>
-    <row r="703" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="5:6" ht="17.25" customHeight="1">
       <c r="E703" s="1"/>
       <c r="F703" s="1"/>
     </row>
-    <row r="704" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="5:6" ht="17.25" customHeight="1">
       <c r="E704" s="1"/>
       <c r="F704" s="1"/>
     </row>
-    <row r="705" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="5:6" ht="17.25" customHeight="1">
       <c r="E705" s="1"/>
       <c r="F705" s="1"/>
     </row>
-    <row r="706" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="5:6" ht="17.25" customHeight="1">
       <c r="E706" s="1"/>
       <c r="F706" s="1"/>
     </row>
-    <row r="707" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="5:6" ht="17.25" customHeight="1">
       <c r="E707" s="1"/>
       <c r="F707" s="1"/>
     </row>
-    <row r="708" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="5:6" ht="17.25" customHeight="1">
       <c r="E708" s="1"/>
       <c r="F708" s="1"/>
     </row>
-    <row r="709" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="5:6" ht="17.25" customHeight="1">
       <c r="E709" s="1"/>
       <c r="F709" s="1"/>
     </row>
-    <row r="710" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="5:6" ht="17.25" customHeight="1">
       <c r="E710" s="1"/>
       <c r="F710" s="1"/>
     </row>
-    <row r="711" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="5:6" ht="17.25" customHeight="1">
       <c r="E711" s="1"/>
       <c r="F711" s="1"/>
     </row>
-    <row r="712" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="5:6" ht="17.25" customHeight="1">
       <c r="E712" s="1"/>
       <c r="F712" s="1"/>
     </row>
-    <row r="713" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="5:6" ht="17.25" customHeight="1">
       <c r="E713" s="1"/>
       <c r="F713" s="1"/>
     </row>
-    <row r="714" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="5:6" ht="17.25" customHeight="1">
       <c r="E714" s="1"/>
       <c r="F714" s="1"/>
     </row>
-    <row r="715" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="5:6" ht="17.25" customHeight="1">
       <c r="E715" s="1"/>
       <c r="F715" s="1"/>
     </row>
-    <row r="716" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="5:6" ht="17.25" customHeight="1">
       <c r="E716" s="1"/>
       <c r="F716" s="1"/>
     </row>
-    <row r="717" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="5:6" ht="17.25" customHeight="1">
       <c r="E717" s="1"/>
       <c r="F717" s="1"/>
     </row>
-    <row r="718" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="5:6" ht="17.25" customHeight="1">
       <c r="E718" s="1"/>
       <c r="F718" s="1"/>
     </row>
-    <row r="719" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="5:6" ht="17.25" customHeight="1">
       <c r="E719" s="1"/>
       <c r="F719" s="1"/>
     </row>
-    <row r="720" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="5:6" ht="17.25" customHeight="1">
       <c r="E720" s="1"/>
       <c r="F720" s="1"/>
     </row>
-    <row r="721" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="5:6" ht="17.25" customHeight="1">
       <c r="E721" s="1"/>
       <c r="F721" s="1"/>
     </row>
-    <row r="722" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="5:6" ht="17.25" customHeight="1">
       <c r="E722" s="1"/>
       <c r="F722" s="1"/>
     </row>
-    <row r="723" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="5:6" ht="17.25" customHeight="1">
       <c r="E723" s="1"/>
       <c r="F723" s="1"/>
     </row>
-    <row r="724" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="5:6" ht="17.25" customHeight="1">
       <c r="E724" s="1"/>
       <c r="F724" s="1"/>
     </row>
-    <row r="725" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="5:6" ht="17.25" customHeight="1">
       <c r="E725" s="1"/>
       <c r="F725" s="1"/>
     </row>
-    <row r="726" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="5:6" ht="17.25" customHeight="1">
       <c r="E726" s="1"/>
       <c r="F726" s="1"/>
     </row>
-    <row r="727" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="5:6" ht="17.25" customHeight="1">
       <c r="E727" s="1"/>
       <c r="F727" s="1"/>
     </row>
-    <row r="728" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="5:6" ht="17.25" customHeight="1">
       <c r="E728" s="1"/>
       <c r="F728" s="1"/>
     </row>
-    <row r="729" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="5:6" ht="17.25" customHeight="1">
       <c r="E729" s="1"/>
       <c r="F729" s="1"/>
     </row>
-    <row r="730" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="5:6" ht="17.25" customHeight="1">
       <c r="E730" s="1"/>
       <c r="F730" s="1"/>
     </row>
-    <row r="731" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="5:6" ht="17.25" customHeight="1">
       <c r="E731" s="1"/>
       <c r="F731" s="1"/>
     </row>
-    <row r="732" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="5:6" ht="17.25" customHeight="1">
       <c r="E732" s="1"/>
       <c r="F732" s="1"/>
     </row>
-    <row r="733" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="5:6" ht="17.25" customHeight="1">
       <c r="E733" s="1"/>
       <c r="F733" s="1"/>
     </row>
-    <row r="734" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="5:6" ht="17.25" customHeight="1">
       <c r="E734" s="1"/>
       <c r="F734" s="1"/>
     </row>
-    <row r="735" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="5:6" ht="17.25" customHeight="1">
       <c r="E735" s="1"/>
       <c r="F735" s="1"/>
     </row>
-    <row r="736" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="5:6" ht="17.25" customHeight="1">
       <c r="E736" s="1"/>
       <c r="F736" s="1"/>
     </row>
-    <row r="737" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="5:6" ht="17.25" customHeight="1">
       <c r="E737" s="1"/>
       <c r="F737" s="1"/>
     </row>
-    <row r="738" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="5:6" ht="17.25" customHeight="1">
       <c r="E738" s="1"/>
       <c r="F738" s="1"/>
     </row>
-    <row r="739" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="5:6" ht="17.25" customHeight="1">
       <c r="E739" s="1"/>
       <c r="F739" s="1"/>
     </row>
-    <row r="740" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="5:6" ht="17.25" customHeight="1">
       <c r="E740" s="1"/>
       <c r="F740" s="1"/>
     </row>
-    <row r="741" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="5:6" ht="17.25" customHeight="1">
       <c r="E741" s="1"/>
       <c r="F741" s="1"/>
     </row>
-    <row r="742" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="5:6" ht="17.25" customHeight="1">
       <c r="E742" s="1"/>
       <c r="F742" s="1"/>
     </row>
-    <row r="743" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="5:6" ht="17.25" customHeight="1">
       <c r="E743" s="1"/>
       <c r="F743" s="1"/>
     </row>
-    <row r="744" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="5:6" ht="17.25" customHeight="1">
       <c r="E744" s="1"/>
       <c r="F744" s="1"/>
     </row>
-    <row r="745" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="5:6" ht="17.25" customHeight="1">
       <c r="E745" s="1"/>
       <c r="F745" s="1"/>
     </row>
-    <row r="746" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="5:6" ht="17.25" customHeight="1">
       <c r="E746" s="1"/>
       <c r="F746" s="1"/>
     </row>
-    <row r="747" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="5:6" ht="17.25" customHeight="1">
       <c r="E747" s="1"/>
       <c r="F747" s="1"/>
     </row>
-    <row r="748" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="5:6" ht="17.25" customHeight="1">
       <c r="E748" s="1"/>
       <c r="F748" s="1"/>
     </row>
-    <row r="749" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="5:6" ht="17.25" customHeight="1">
       <c r="E749" s="1"/>
       <c r="F749" s="1"/>
     </row>
-    <row r="750" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="5:6" ht="17.25" customHeight="1">
       <c r="E750" s="1"/>
       <c r="F750" s="1"/>
     </row>
-    <row r="751" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="5:6" ht="17.25" customHeight="1">
       <c r="E751" s="1"/>
       <c r="F751" s="1"/>
     </row>
-    <row r="752" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="5:6" ht="17.25" customHeight="1">
       <c r="E752" s="1"/>
       <c r="F752" s="1"/>
     </row>
-    <row r="753" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="5:6" ht="17.25" customHeight="1">
       <c r="E753" s="1"/>
       <c r="F753" s="1"/>
     </row>
-    <row r="754" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="5:6" ht="17.25" customHeight="1">
       <c r="E754" s="1"/>
       <c r="F754" s="1"/>
     </row>
-    <row r="755" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="5:6" ht="17.25" customHeight="1">
       <c r="E755" s="1"/>
       <c r="F755" s="1"/>
     </row>
-    <row r="756" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="5:6" ht="17.25" customHeight="1">
       <c r="E756" s="1"/>
       <c r="F756" s="1"/>
     </row>
-    <row r="757" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="5:6" ht="17.25" customHeight="1">
       <c r="E757" s="1"/>
       <c r="F757" s="1"/>
     </row>
-    <row r="758" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="5:6" ht="17.25" customHeight="1">
       <c r="E758" s="1"/>
       <c r="F758" s="1"/>
     </row>
-    <row r="759" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="5:6" ht="17.25" customHeight="1">
       <c r="E759" s="1"/>
       <c r="F759" s="1"/>
     </row>
-    <row r="760" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="5:6" ht="17.25" customHeight="1">
       <c r="E760" s="1"/>
       <c r="F760" s="1"/>
     </row>
-    <row r="761" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="5:6" ht="17.25" customHeight="1">
       <c r="E761" s="1"/>
       <c r="F761" s="1"/>
     </row>
-    <row r="762" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="5:6" ht="17.25" customHeight="1">
       <c r="E762" s="1"/>
       <c r="F762" s="1"/>
     </row>
-    <row r="763" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="5:6" ht="17.25" customHeight="1">
       <c r="E763" s="1"/>
       <c r="F763" s="1"/>
     </row>
-    <row r="764" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="5:6" ht="17.25" customHeight="1">
       <c r="E764" s="1"/>
       <c r="F764" s="1"/>
     </row>
-    <row r="765" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="5:6" ht="17.25" customHeight="1">
       <c r="E765" s="1"/>
       <c r="F765" s="1"/>
     </row>
-    <row r="766" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="5:6" ht="17.25" customHeight="1">
       <c r="E766" s="1"/>
       <c r="F766" s="1"/>
     </row>
-    <row r="767" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="5:6" ht="17.25" customHeight="1">
       <c r="E767" s="1"/>
       <c r="F767" s="1"/>
     </row>
-    <row r="768" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="5:6" ht="17.25" customHeight="1">
       <c r="E768" s="1"/>
       <c r="F768" s="1"/>
     </row>
-    <row r="769" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="5:6" ht="17.25" customHeight="1">
       <c r="E769" s="1"/>
       <c r="F769" s="1"/>
     </row>
-    <row r="770" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="5:6" ht="17.25" customHeight="1">
       <c r="E770" s="1"/>
       <c r="F770" s="1"/>
     </row>
-    <row r="771" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="5:6" ht="17.25" customHeight="1">
       <c r="E771" s="1"/>
       <c r="F771" s="1"/>
     </row>
-    <row r="772" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="5:6" ht="17.25" customHeight="1">
       <c r="E772" s="1"/>
       <c r="F772" s="1"/>
     </row>
-    <row r="773" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="5:6" ht="17.25" customHeight="1">
       <c r="E773" s="1"/>
       <c r="F773" s="1"/>
     </row>
-    <row r="774" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="5:6" ht="17.25" customHeight="1">
       <c r="E774" s="1"/>
       <c r="F774" s="1"/>
     </row>
-    <row r="775" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="5:6" ht="17.25" customHeight="1">
       <c r="E775" s="1"/>
       <c r="F775" s="1"/>
     </row>
-    <row r="776" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="5:6" ht="17.25" customHeight="1">
       <c r="E776" s="1"/>
       <c r="F776" s="1"/>
     </row>
-    <row r="777" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="5:6" ht="17.25" customHeight="1">
       <c r="E777" s="1"/>
       <c r="F777" s="1"/>
     </row>
-    <row r="778" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="5:6" ht="17.25" customHeight="1">
       <c r="E778" s="1"/>
       <c r="F778" s="1"/>
     </row>
-    <row r="779" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="5:6" ht="17.25" customHeight="1">
       <c r="E779" s="1"/>
       <c r="F779" s="1"/>
     </row>
-    <row r="780" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="5:6" ht="17.25" customHeight="1">
       <c r="E780" s="1"/>
       <c r="F780" s="1"/>
     </row>
-    <row r="781" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="5:6" ht="17.25" customHeight="1">
       <c r="E781" s="1"/>
       <c r="F781" s="1"/>
     </row>
-    <row r="782" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="5:6" ht="17.25" customHeight="1">
       <c r="E782" s="1"/>
       <c r="F782" s="1"/>
     </row>
-    <row r="783" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="5:6" ht="17.25" customHeight="1">
       <c r="E783" s="1"/>
       <c r="F783" s="1"/>
     </row>
-    <row r="784" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="5:6" ht="17.25" customHeight="1">
       <c r="E784" s="1"/>
       <c r="F784" s="1"/>
     </row>
-    <row r="785" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="5:6" ht="17.25" customHeight="1">
       <c r="E785" s="1"/>
       <c r="F785" s="1"/>
     </row>
-    <row r="786" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="5:6" ht="17.25" customHeight="1">
       <c r="E786" s="1"/>
       <c r="F786" s="1"/>
     </row>
-    <row r="787" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="5:6" ht="17.25" customHeight="1">
       <c r="E787" s="1"/>
       <c r="F787" s="1"/>
     </row>
-    <row r="788" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="5:6" ht="17.25" customHeight="1">
       <c r="E788" s="1"/>
       <c r="F788" s="1"/>
     </row>
-    <row r="789" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="5:6" ht="17.25" customHeight="1">
       <c r="E789" s="1"/>
       <c r="F789" s="1"/>
     </row>
-    <row r="790" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="5:6" ht="17.25" customHeight="1">
       <c r="E790" s="1"/>
       <c r="F790" s="1"/>
     </row>
-    <row r="791" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="5:6" ht="17.25" customHeight="1">
       <c r="E791" s="1"/>
       <c r="F791" s="1"/>
     </row>
-    <row r="792" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="5:6" ht="17.25" customHeight="1">
       <c r="E792" s="1"/>
       <c r="F792" s="1"/>
     </row>
-    <row r="793" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="5:6" ht="17.25" customHeight="1">
       <c r="E793" s="1"/>
       <c r="F793" s="1"/>
     </row>
-    <row r="794" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="5:6" ht="17.25" customHeight="1">
       <c r="E794" s="1"/>
       <c r="F794" s="1"/>
     </row>
-    <row r="795" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="5:6" ht="17.25" customHeight="1">
       <c r="E795" s="1"/>
       <c r="F795" s="1"/>
     </row>
-    <row r="796" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="5:6" ht="17.25" customHeight="1">
       <c r="E796" s="1"/>
       <c r="F796" s="1"/>
     </row>
-    <row r="797" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="5:6" ht="17.25" customHeight="1">
       <c r="E797" s="1"/>
       <c r="F797" s="1"/>
     </row>
-    <row r="798" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="5:6" ht="17.25" customHeight="1">
       <c r="E798" s="1"/>
       <c r="F798" s="1"/>
     </row>
-    <row r="799" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="5:6" ht="17.25" customHeight="1">
       <c r="E799" s="1"/>
       <c r="F799" s="1"/>
     </row>
-    <row r="800" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="5:6" ht="17.25" customHeight="1">
       <c r="E800" s="1"/>
       <c r="F800" s="1"/>
     </row>
-    <row r="801" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="5:6" ht="17.25" customHeight="1">
       <c r="E801" s="1"/>
       <c r="F801" s="1"/>
     </row>
-    <row r="802" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="5:6" ht="17.25" customHeight="1">
       <c r="E802" s="1"/>
       <c r="F802" s="1"/>
     </row>
-    <row r="803" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="5:6" ht="17.25" customHeight="1">
       <c r="E803" s="1"/>
       <c r="F803" s="1"/>
     </row>
-    <row r="804" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="5:6" ht="17.25" customHeight="1">
       <c r="E804" s="1"/>
       <c r="F804" s="1"/>
     </row>
-    <row r="805" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="5:6" ht="17.25" customHeight="1">
       <c r="E805" s="1"/>
       <c r="F805" s="1"/>
     </row>
-    <row r="806" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="5:6" ht="17.25" customHeight="1">
       <c r="E806" s="1"/>
       <c r="F806" s="1"/>
     </row>
-    <row r="807" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="5:6" ht="17.25" customHeight="1">
       <c r="E807" s="1"/>
       <c r="F807" s="1"/>
     </row>
-    <row r="808" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="5:6" ht="17.25" customHeight="1">
       <c r="E808" s="1"/>
       <c r="F808" s="1"/>
     </row>
-    <row r="809" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="5:6" ht="17.25" customHeight="1">
       <c r="E809" s="1"/>
       <c r="F809" s="1"/>
     </row>
-    <row r="810" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="5:6" ht="17.25" customHeight="1">
       <c r="E810" s="1"/>
       <c r="F810" s="1"/>
     </row>
-    <row r="811" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="5:6" ht="17.25" customHeight="1">
       <c r="E811" s="1"/>
       <c r="F811" s="1"/>
     </row>
-    <row r="812" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="5:6" ht="17.25" customHeight="1">
       <c r="E812" s="1"/>
       <c r="F812" s="1"/>
     </row>
-    <row r="813" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="5:6" ht="17.25" customHeight="1">
       <c r="E813" s="1"/>
       <c r="F813" s="1"/>
     </row>
-    <row r="814" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="5:6" ht="17.25" customHeight="1">
       <c r="E814" s="1"/>
       <c r="F814" s="1"/>
     </row>
-    <row r="815" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="5:6" ht="17.25" customHeight="1">
       <c r="E815" s="1"/>
       <c r="F815" s="1"/>
     </row>
-    <row r="816" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="5:6" ht="17.25" customHeight="1">
       <c r="E816" s="1"/>
       <c r="F816" s="1"/>
     </row>
-    <row r="817" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="5:6" ht="17.25" customHeight="1">
       <c r="E817" s="1"/>
       <c r="F817" s="1"/>
     </row>
-    <row r="818" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="5:6" ht="17.25" customHeight="1">
       <c r="E818" s="1"/>
       <c r="F818" s="1"/>
     </row>
-    <row r="819" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="5:6" ht="17.25" customHeight="1">
       <c r="E819" s="1"/>
       <c r="F819" s="1"/>
     </row>
-    <row r="820" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="5:6" ht="17.25" customHeight="1">
       <c r="E820" s="1"/>
       <c r="F820" s="1"/>
     </row>
-    <row r="821" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="5:6" ht="17.25" customHeight="1">
       <c r="E821" s="1"/>
       <c r="F821" s="1"/>
     </row>
-    <row r="822" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="5:6" ht="17.25" customHeight="1">
       <c r="E822" s="1"/>
       <c r="F822" s="1"/>
     </row>
-    <row r="823" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="5:6" ht="17.25" customHeight="1">
       <c r="E823" s="1"/>
       <c r="F823" s="1"/>
     </row>
-    <row r="824" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="5:6" ht="17.25" customHeight="1">
       <c r="E824" s="1"/>
       <c r="F824" s="1"/>
     </row>
-    <row r="825" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="5:6" ht="17.25" customHeight="1">
       <c r="E825" s="1"/>
       <c r="F825" s="1"/>
     </row>
-    <row r="826" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="5:6" ht="17.25" customHeight="1">
       <c r="E826" s="1"/>
       <c r="F826" s="1"/>
     </row>
-    <row r="827" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="5:6" ht="17.25" customHeight="1">
       <c r="E827" s="1"/>
       <c r="F827" s="1"/>
     </row>
-    <row r="828" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="5:6" ht="17.25" customHeight="1">
       <c r="E828" s="1"/>
       <c r="F828" s="1"/>
     </row>
-    <row r="829" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="5:6" ht="17.25" customHeight="1">
       <c r="E829" s="1"/>
       <c r="F829" s="1"/>
     </row>
-    <row r="830" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="5:6" ht="17.25" customHeight="1">
       <c r="E830" s="1"/>
       <c r="F830" s="1"/>
     </row>
-    <row r="831" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="5:6" ht="17.25" customHeight="1">
       <c r="E831" s="1"/>
       <c r="F831" s="1"/>
     </row>
-    <row r="832" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="5:6" ht="17.25" customHeight="1">
       <c r="E832" s="1"/>
       <c r="F832" s="1"/>
     </row>
-    <row r="833" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="5:6" ht="17.25" customHeight="1">
       <c r="E833" s="1"/>
       <c r="F833" s="1"/>
     </row>
-    <row r="834" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="5:6" ht="17.25" customHeight="1">
       <c r="E834" s="1"/>
       <c r="F834" s="1"/>
     </row>
-    <row r="835" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="5:6" ht="17.25" customHeight="1">
       <c r="E835" s="1"/>
       <c r="F835" s="1"/>
     </row>
-    <row r="836" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="5:6" ht="17.25" customHeight="1">
       <c r="E836" s="1"/>
       <c r="F836" s="1"/>
     </row>
-    <row r="837" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="5:6" ht="17.25" customHeight="1">
       <c r="E837" s="1"/>
       <c r="F837" s="1"/>
     </row>
-    <row r="838" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="5:6" ht="17.25" customHeight="1">
       <c r="E838" s="1"/>
       <c r="F838" s="1"/>
     </row>
-    <row r="839" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="5:6" ht="17.25" customHeight="1">
       <c r="E839" s="1"/>
       <c r="F839" s="1"/>
     </row>
-    <row r="840" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="5:6" ht="17.25" customHeight="1">
       <c r="E840" s="1"/>
       <c r="F840" s="1"/>
     </row>
-    <row r="841" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="5:6" ht="17.25" customHeight="1">
       <c r="E841" s="1"/>
       <c r="F841" s="1"/>
     </row>
-    <row r="842" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="5:6" ht="17.25" customHeight="1">
       <c r="E842" s="1"/>
       <c r="F842" s="1"/>
     </row>
-    <row r="843" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="5:6" ht="17.25" customHeight="1">
       <c r="E843" s="1"/>
       <c r="F843" s="1"/>
     </row>
-    <row r="844" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="5:6" ht="17.25" customHeight="1">
       <c r="E844" s="1"/>
       <c r="F844" s="1"/>
     </row>
-    <row r="845" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="5:6" ht="17.25" customHeight="1">
       <c r="E845" s="1"/>
       <c r="F845" s="1"/>
     </row>
-    <row r="846" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="5:6" ht="17.25" customHeight="1">
       <c r="E846" s="1"/>
       <c r="F846" s="1"/>
     </row>
-    <row r="847" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="5:6" ht="17.25" customHeight="1">
       <c r="E847" s="1"/>
       <c r="F847" s="1"/>
     </row>
-    <row r="848" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="5:6" ht="17.25" customHeight="1">
       <c r="E848" s="1"/>
       <c r="F848" s="1"/>
     </row>
-    <row r="849" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="5:6" ht="17.25" customHeight="1">
       <c r="E849" s="1"/>
       <c r="F849" s="1"/>
     </row>
-    <row r="850" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="5:6" ht="17.25" customHeight="1">
       <c r="E850" s="1"/>
       <c r="F850" s="1"/>
     </row>
-    <row r="851" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="5:6" ht="17.25" customHeight="1">
       <c r="E851" s="1"/>
       <c r="F851" s="1"/>
     </row>
-    <row r="852" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="5:6" ht="17.25" customHeight="1">
       <c r="E852" s="1"/>
       <c r="F852" s="1"/>
     </row>
-    <row r="853" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="5:6" ht="17.25" customHeight="1">
       <c r="E853" s="1"/>
       <c r="F853" s="1"/>
     </row>
-    <row r="854" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="5:6" ht="17.25" customHeight="1">
       <c r="E854" s="1"/>
       <c r="F854" s="1"/>
     </row>
-    <row r="855" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="5:6" ht="17.25" customHeight="1">
       <c r="E855" s="1"/>
       <c r="F855" s="1"/>
     </row>
-    <row r="856" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="5:6" ht="17.25" customHeight="1">
       <c r="E856" s="1"/>
       <c r="F856" s="1"/>
     </row>
-    <row r="857" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="5:6" ht="17.25" customHeight="1">
       <c r="E857" s="1"/>
       <c r="F857" s="1"/>
     </row>
-    <row r="858" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="5:6" ht="17.25" customHeight="1">
       <c r="E858" s="1"/>
       <c r="F858" s="1"/>
     </row>
-    <row r="859" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="5:6" ht="17.25" customHeight="1">
       <c r="E859" s="1"/>
       <c r="F859" s="1"/>
     </row>
-    <row r="860" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="5:6" ht="17.25" customHeight="1">
       <c r="E860" s="1"/>
       <c r="F860" s="1"/>
     </row>
-    <row r="861" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="5:6" ht="17.25" customHeight="1">
       <c r="E861" s="1"/>
       <c r="F861" s="1"/>
     </row>
-    <row r="862" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="5:6" ht="17.25" customHeight="1">
       <c r="E862" s="1"/>
       <c r="F862" s="1"/>
     </row>
-    <row r="863" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="5:6" ht="17.25" customHeight="1">
       <c r="E863" s="1"/>
       <c r="F863" s="1"/>
     </row>
-    <row r="864" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="5:6" ht="17.25" customHeight="1">
       <c r="E864" s="1"/>
       <c r="F864" s="1"/>
     </row>
-    <row r="865" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="5:6" ht="17.25" customHeight="1">
       <c r="E865" s="1"/>
       <c r="F865" s="1"/>
     </row>
-    <row r="866" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="5:6" ht="17.25" customHeight="1">
       <c r="E866" s="1"/>
       <c r="F866" s="1"/>
     </row>
-    <row r="867" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="5:6" ht="17.25" customHeight="1">
       <c r="E867" s="1"/>
       <c r="F867" s="1"/>
     </row>
-    <row r="868" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="5:6" ht="17.25" customHeight="1">
       <c r="E868" s="1"/>
       <c r="F868" s="1"/>
     </row>
-    <row r="869" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="5:6" ht="17.25" customHeight="1">
       <c r="E869" s="1"/>
       <c r="F869" s="1"/>
     </row>
-    <row r="870" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="5:6" ht="17.25" customHeight="1">
       <c r="E870" s="1"/>
       <c r="F870" s="1"/>
     </row>
-    <row r="871" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="5:6" ht="17.25" customHeight="1">
       <c r="E871" s="1"/>
       <c r="F871" s="1"/>
     </row>
-    <row r="872" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="5:6" ht="17.25" customHeight="1">
       <c r="E872" s="1"/>
       <c r="F872" s="1"/>
     </row>
-    <row r="873" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="5:6" ht="17.25" customHeight="1">
       <c r="E873" s="1"/>
       <c r="F873" s="1"/>
     </row>
-    <row r="874" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="5:6" ht="17.25" customHeight="1">
       <c r="E874" s="1"/>
       <c r="F874" s="1"/>
     </row>
-    <row r="875" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="5:6" ht="17.25" customHeight="1">
       <c r="E875" s="1"/>
       <c r="F875" s="1"/>
     </row>
-    <row r="876" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="5:6" ht="17.25" customHeight="1">
       <c r="E876" s="1"/>
       <c r="F876" s="1"/>
     </row>
-    <row r="877" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="5:6" ht="17.25" customHeight="1">
       <c r="E877" s="1"/>
       <c r="F877" s="1"/>
     </row>
-    <row r="878" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="5:6" ht="17.25" customHeight="1">
       <c r="E878" s="1"/>
       <c r="F878" s="1"/>
     </row>
-    <row r="879" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="5:6" ht="17.25" customHeight="1">
       <c r="E879" s="1"/>
       <c r="F879" s="1"/>
     </row>
-    <row r="880" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="5:6" ht="17.25" customHeight="1">
       <c r="E880" s="1"/>
       <c r="F880" s="1"/>
     </row>
-    <row r="881" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="5:6" ht="17.25" customHeight="1">
       <c r="E881" s="1"/>
       <c r="F881" s="1"/>
     </row>
-    <row r="882" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="5:6" ht="17.25" customHeight="1">
       <c r="E882" s="1"/>
       <c r="F882" s="1"/>
     </row>
-    <row r="883" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="5:6" ht="17.25" customHeight="1">
       <c r="E883" s="1"/>
       <c r="F883" s="1"/>
     </row>
-    <row r="884" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="5:6" ht="17.25" customHeight="1">
       <c r="E884" s="1"/>
       <c r="F884" s="1"/>
     </row>
-    <row r="885" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="5:6" ht="17.25" customHeight="1">
       <c r="E885" s="1"/>
       <c r="F885" s="1"/>
     </row>
-    <row r="886" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="5:6" ht="17.25" customHeight="1">
       <c r="E886" s="1"/>
       <c r="F886" s="1"/>
     </row>
-    <row r="887" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="5:6" ht="17.25" customHeight="1">
       <c r="E887" s="1"/>
       <c r="F887" s="1"/>
     </row>
-    <row r="888" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="5:6" ht="17.25" customHeight="1">
       <c r="E888" s="1"/>
       <c r="F888" s="1"/>
     </row>
-    <row r="889" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="5:6" ht="17.25" customHeight="1">
       <c r="E889" s="1"/>
       <c r="F889" s="1"/>
     </row>
-    <row r="890" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="5:6" ht="17.25" customHeight="1">
       <c r="E890" s="1"/>
       <c r="F890" s="1"/>
     </row>
-    <row r="891" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="5:6" ht="17.25" customHeight="1">
       <c r="E891" s="1"/>
       <c r="F891" s="1"/>
     </row>
-    <row r="892" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="5:6" ht="17.25" customHeight="1">
       <c r="E892" s="1"/>
       <c r="F892" s="1"/>
     </row>
-    <row r="893" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="5:6" ht="17.25" customHeight="1">
       <c r="E893" s="1"/>
       <c r="F893" s="1"/>
     </row>
-    <row r="894" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="5:6" ht="17.25" customHeight="1">
       <c r="E894" s="1"/>
       <c r="F894" s="1"/>
     </row>
-    <row r="895" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="5:6" ht="17.25" customHeight="1">
       <c r="E895" s="1"/>
       <c r="F895" s="1"/>
     </row>
-    <row r="896" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="5:6" ht="17.25" customHeight="1">
       <c r="E896" s="1"/>
       <c r="F896" s="1"/>
     </row>
-    <row r="897" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="5:6" ht="17.25" customHeight="1">
       <c r="E897" s="1"/>
       <c r="F897" s="1"/>
     </row>
-    <row r="898" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="5:6" ht="17.25" customHeight="1">
       <c r="E898" s="1"/>
       <c r="F898" s="1"/>
     </row>
-    <row r="899" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="5:6" ht="17.25" customHeight="1">
       <c r="E899" s="1"/>
       <c r="F899" s="1"/>
     </row>
-    <row r="900" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="5:6" ht="17.25" customHeight="1">
       <c r="E900" s="1"/>
       <c r="F900" s="1"/>
     </row>
-    <row r="901" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="5:6" ht="17.25" customHeight="1">
       <c r="E901" s="1"/>
       <c r="F901" s="1"/>
     </row>
-    <row r="902" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="5:6" ht="17.25" customHeight="1">
       <c r="E902" s="1"/>
       <c r="F902" s="1"/>
     </row>
-    <row r="903" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="5:6" ht="17.25" customHeight="1">
       <c r="E903" s="1"/>
       <c r="F903" s="1"/>
     </row>
-    <row r="904" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="5:6" ht="17.25" customHeight="1">
       <c r="E904" s="1"/>
       <c r="F904" s="1"/>
     </row>
-    <row r="905" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="5:6" ht="17.25" customHeight="1">
       <c r="E905" s="1"/>
       <c r="F905" s="1"/>
     </row>
-    <row r="906" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="5:6" ht="17.25" customHeight="1">
       <c r="E906" s="1"/>
       <c r="F906" s="1"/>
     </row>
-    <row r="907" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="5:6" ht="17.25" customHeight="1">
       <c r="E907" s="1"/>
       <c r="F907" s="1"/>
     </row>
-    <row r="908" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="5:6" ht="17.25" customHeight="1">
       <c r="E908" s="1"/>
       <c r="F908" s="1"/>
     </row>
-    <row r="909" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="5:6" ht="17.25" customHeight="1">
       <c r="E909" s="1"/>
       <c r="F909" s="1"/>
     </row>
-    <row r="910" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="5:6" ht="17.25" customHeight="1">
       <c r="E910" s="1"/>
       <c r="F910" s="1"/>
     </row>
-    <row r="911" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="5:6" ht="17.25" customHeight="1">
       <c r="E911" s="1"/>
       <c r="F911" s="1"/>
     </row>
-    <row r="912" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="5:6" ht="17.25" customHeight="1">
       <c r="E912" s="1"/>
       <c r="F912" s="1"/>
     </row>
-    <row r="913" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="5:6" ht="17.25" customHeight="1">
       <c r="E913" s="1"/>
       <c r="F913" s="1"/>
     </row>
-    <row r="914" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="5:6" ht="17.25" customHeight="1">
       <c r="E914" s="1"/>
       <c r="F914" s="1"/>
     </row>
-    <row r="915" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="5:6" ht="17.25" customHeight="1">
       <c r="E915" s="1"/>
       <c r="F915" s="1"/>
     </row>
-    <row r="916" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="5:6" ht="17.25" customHeight="1">
       <c r="E916" s="1"/>
       <c r="F916" s="1"/>
     </row>
-    <row r="917" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="5:6" ht="17.25" customHeight="1">
       <c r="E917" s="1"/>
       <c r="F917" s="1"/>
     </row>
-    <row r="918" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="5:6" ht="17.25" customHeight="1">
       <c r="E918" s="1"/>
       <c r="F918" s="1"/>
     </row>
-    <row r="919" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="5:6" ht="17.25" customHeight="1">
       <c r="E919" s="1"/>
       <c r="F919" s="1"/>
     </row>
-    <row r="920" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="5:6" ht="17.25" customHeight="1">
       <c r="E920" s="1"/>
       <c r="F920" s="1"/>
     </row>
-    <row r="921" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="5:6" ht="17.25" customHeight="1">
       <c r="E921" s="1"/>
       <c r="F921" s="1"/>
     </row>
-    <row r="922" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="5:6" ht="17.25" customHeight="1">
       <c r="E922" s="1"/>
       <c r="F922" s="1"/>
     </row>
-    <row r="923" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="5:6" ht="17.25" customHeight="1">
       <c r="E923" s="1"/>
       <c r="F923" s="1"/>
     </row>
-    <row r="924" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="5:6" ht="17.25" customHeight="1">
       <c r="E924" s="1"/>
       <c r="F924" s="1"/>
     </row>
-    <row r="925" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="5:6" ht="17.25" customHeight="1">
       <c r="E925" s="1"/>
       <c r="F925" s="1"/>
     </row>
-    <row r="926" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="5:6" ht="17.25" customHeight="1">
       <c r="E926" s="1"/>
       <c r="F926" s="1"/>
     </row>
-    <row r="927" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="5:6" ht="17.25" customHeight="1">
       <c r="E927" s="1"/>
       <c r="F927" s="1"/>
     </row>
-    <row r="928" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="5:6" ht="17.25" customHeight="1">
       <c r="E928" s="1"/>
       <c r="F928" s="1"/>
     </row>
-    <row r="929" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="5:6" ht="17.25" customHeight="1">
       <c r="E929" s="1"/>
       <c r="F929" s="1"/>
     </row>
-    <row r="930" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="5:6" ht="17.25" customHeight="1">
       <c r="E930" s="1"/>
       <c r="F930" s="1"/>
     </row>
-    <row r="931" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="5:6" ht="17.25" customHeight="1">
       <c r="E931" s="1"/>
       <c r="F931" s="1"/>
     </row>
-    <row r="932" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="5:6" ht="17.25" customHeight="1">
       <c r="E932" s="1"/>
       <c r="F932" s="1"/>
     </row>
-    <row r="933" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="5:6" ht="17.25" customHeight="1">
       <c r="E933" s="1"/>
       <c r="F933" s="1"/>
     </row>
-    <row r="934" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="5:6" ht="17.25" customHeight="1">
       <c r="E934" s="1"/>
       <c r="F934" s="1"/>
     </row>
-    <row r="935" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="5:6" ht="17.25" customHeight="1">
       <c r="E935" s="1"/>
       <c r="F935" s="1"/>
     </row>
-    <row r="936" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="5:6" ht="17.25" customHeight="1">
       <c r="E936" s="1"/>
       <c r="F936" s="1"/>
     </row>
-    <row r="937" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="5:6" ht="17.25" customHeight="1">
       <c r="E937" s="1"/>
       <c r="F937" s="1"/>
     </row>
-    <row r="938" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="5:6" ht="17.25" customHeight="1">
       <c r="E938" s="1"/>
       <c r="F938" s="1"/>
     </row>
-    <row r="939" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="5:6" ht="17.25" customHeight="1">
       <c r="E939" s="1"/>
       <c r="F939" s="1"/>
     </row>
-    <row r="940" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="5:6" ht="17.25" customHeight="1">
       <c r="E940" s="1"/>
       <c r="F940" s="1"/>
     </row>
-    <row r="941" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="5:6" ht="17.25" customHeight="1">
       <c r="E941" s="1"/>
       <c r="F941" s="1"/>
     </row>
-    <row r="942" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="5:6" ht="17.25" customHeight="1">
       <c r="E942" s="1"/>
       <c r="F942" s="1"/>
     </row>
-    <row r="943" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="5:6" ht="17.25" customHeight="1">
       <c r="E943" s="1"/>
       <c r="F943" s="1"/>
     </row>
-    <row r="944" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="5:6" ht="17.25" customHeight="1">
       <c r="E944" s="1"/>
       <c r="F944" s="1"/>
     </row>
-    <row r="945" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="5:6" ht="17.25" customHeight="1">
       <c r="E945" s="1"/>
       <c r="F945" s="1"/>
     </row>
-    <row r="946" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="5:6" ht="17.25" customHeight="1">
       <c r="E946" s="1"/>
       <c r="F946" s="1"/>
     </row>
-    <row r="947" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="5:6" ht="17.25" customHeight="1">
       <c r="E947" s="1"/>
       <c r="F947" s="1"/>
     </row>
-    <row r="948" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="5:6" ht="17.25" customHeight="1">
       <c r="E948" s="1"/>
       <c r="F948" s="1"/>
     </row>
-    <row r="949" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="5:6" ht="17.25" customHeight="1">
       <c r="E949" s="1"/>
       <c r="F949" s="1"/>
     </row>
-    <row r="950" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="5:6" ht="17.25" customHeight="1">
       <c r="E950" s="1"/>
       <c r="F950" s="1"/>
     </row>
-    <row r="951" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="5:6" ht="17.25" customHeight="1">
       <c r="E951" s="1"/>
       <c r="F951" s="1"/>
     </row>
-    <row r="952" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="5:6" ht="17.25" customHeight="1">
       <c r="E952" s="1"/>
       <c r="F952" s="1"/>
     </row>
-    <row r="953" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="5:6" ht="17.25" customHeight="1">
       <c r="E953" s="1"/>
       <c r="F953" s="1"/>
     </row>
-    <row r="954" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="5:6" ht="17.25" customHeight="1">
       <c r="E954" s="1"/>
       <c r="F954" s="1"/>
     </row>
-    <row r="955" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="5:6" ht="17.25" customHeight="1">
       <c r="E955" s="1"/>
       <c r="F955" s="1"/>
     </row>
-    <row r="956" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="5:6" ht="17.25" customHeight="1">
       <c r="E956" s="1"/>
       <c r="F956" s="1"/>
     </row>
-    <row r="957" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="5:6" ht="17.25" customHeight="1">
       <c r="E957" s="1"/>
       <c r="F957" s="1"/>
     </row>
-    <row r="958" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="5:6" ht="17.25" customHeight="1">
       <c r="E958" s="1"/>
       <c r="F958" s="1"/>
     </row>
-    <row r="959" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="5:6" ht="17.25" customHeight="1">
       <c r="E959" s="1"/>
       <c r="F959" s="1"/>
     </row>
-    <row r="960" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="5:6" ht="17.25" customHeight="1">
       <c r="E960" s="1"/>
       <c r="F960" s="1"/>
     </row>
-    <row r="961" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="5:6" ht="17.25" customHeight="1">
       <c r="E961" s="1"/>
       <c r="F961" s="1"/>
     </row>
-    <row r="962" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="5:6" ht="17.25" customHeight="1">
       <c r="E962" s="1"/>
       <c r="F962" s="1"/>
     </row>
-    <row r="963" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="5:6" ht="17.25" customHeight="1">
       <c r="E963" s="1"/>
       <c r="F963" s="1"/>
     </row>
-    <row r="964" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="5:6" ht="17.25" customHeight="1">
       <c r="E964" s="1"/>
       <c r="F964" s="1"/>
     </row>
-    <row r="965" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="5:6" ht="17.25" customHeight="1">
       <c r="E965" s="1"/>
       <c r="F965" s="1"/>
     </row>
-    <row r="966" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="5:6" ht="17.25" customHeight="1">
       <c r="E966" s="1"/>
       <c r="F966" s="1"/>
     </row>
-    <row r="967" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="5:6" ht="17.25" customHeight="1">
       <c r="E967" s="1"/>
       <c r="F967" s="1"/>
     </row>
-    <row r="968" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="5:6" ht="17.25" customHeight="1">
       <c r="E968" s="1"/>
       <c r="F968" s="1"/>
     </row>
-    <row r="969" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="969" spans="5:6" ht="17.25" customHeight="1">
       <c r="E969" s="1"/>
       <c r="F969" s="1"/>
     </row>
-    <row r="970" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="970" spans="5:6" ht="17.25" customHeight="1">
       <c r="E970" s="1"/>
       <c r="F970" s="1"/>
     </row>
-    <row r="971" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="5:6" ht="17.25" customHeight="1">
       <c r="E971" s="1"/>
       <c r="F971" s="1"/>
     </row>
-    <row r="972" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="972" spans="5:6" ht="17.25" customHeight="1">
       <c r="E972" s="1"/>
       <c r="F972" s="1"/>
     </row>
-    <row r="973" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="5:6" ht="17.25" customHeight="1">
       <c r="E973" s="1"/>
       <c r="F973" s="1"/>
     </row>
-    <row r="974" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="5:6" ht="17.25" customHeight="1">
       <c r="E974" s="1"/>
       <c r="F974" s="1"/>
     </row>
-    <row r="975" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="5:6" ht="17.25" customHeight="1">
       <c r="E975" s="1"/>
       <c r="F975" s="1"/>
     </row>
-    <row r="976" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="5:6" ht="17.25" customHeight="1">
       <c r="E976" s="1"/>
       <c r="F976" s="1"/>
     </row>
-    <row r="977" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="5:6" ht="17.25" customHeight="1">
       <c r="E977" s="1"/>
       <c r="F977" s="1"/>
     </row>
-    <row r="978" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="5:6" ht="17.25" customHeight="1">
       <c r="E978" s="1"/>
       <c r="F978" s="1"/>
     </row>
-    <row r="979" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="5:6" ht="17.25" customHeight="1">
       <c r="E979" s="1"/>
       <c r="F979" s="1"/>
     </row>
-    <row r="980" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="5:6" ht="17.25" customHeight="1">
       <c r="E980" s="1"/>
       <c r="F980" s="1"/>
     </row>
-    <row r="981" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="5:6" ht="17.25" customHeight="1">
       <c r="E981" s="1"/>
       <c r="F981" s="1"/>
     </row>
-    <row r="982" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="5:6" ht="17.25" customHeight="1">
       <c r="E982" s="1"/>
       <c r="F982" s="1"/>
     </row>
-    <row r="983" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="5:6" ht="17.25" customHeight="1">
       <c r="E983" s="1"/>
       <c r="F983" s="1"/>
     </row>
-    <row r="984" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="5:6" ht="17.25" customHeight="1">
       <c r="E984" s="1"/>
       <c r="F984" s="1"/>
     </row>
-    <row r="985" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="5:6" ht="17.25" customHeight="1">
       <c r="E985" s="1"/>
       <c r="F985" s="1"/>
     </row>
-    <row r="986" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="5:6" ht="17.25" customHeight="1">
       <c r="E986" s="1"/>
       <c r="F986" s="1"/>
     </row>
-    <row r="987" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="5:6" ht="17.25" customHeight="1">
       <c r="E987" s="1"/>
       <c r="F987" s="1"/>
     </row>
-    <row r="988" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="5:6" ht="17.25" customHeight="1">
       <c r="E988" s="1"/>
       <c r="F988" s="1"/>
     </row>
-    <row r="989" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="5:6" ht="17.25" customHeight="1">
       <c r="E989" s="1"/>
       <c r="F989" s="1"/>
     </row>
-    <row r="990" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="5:6" ht="17.25" customHeight="1">
       <c r="E990" s="1"/>
       <c r="F990" s="1"/>
     </row>
-    <row r="991" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="5:6" ht="17.25" customHeight="1">
       <c r="E991" s="1"/>
       <c r="F991" s="1"/>
     </row>
-    <row r="992" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="5:6" ht="17.25" customHeight="1">
       <c r="E992" s="1"/>
       <c r="F992" s="1"/>
     </row>
-    <row r="993" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="5:6" ht="17.25" customHeight="1">
       <c r="E993" s="1"/>
       <c r="F993" s="1"/>
     </row>
-    <row r="994" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="5:6" ht="17.25" customHeight="1">
       <c r="E994" s="1"/>
       <c r="F994" s="1"/>
     </row>
-    <row r="995" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="5:6" ht="17.25" customHeight="1">
       <c r="E995" s="1"/>
       <c r="F995" s="1"/>
     </row>
-    <row r="996" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="5:6" ht="17.25" customHeight="1">
       <c r="E996" s="1"/>
       <c r="F996" s="1"/>
     </row>
-    <row r="997" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="5:6" ht="17.25" customHeight="1">
       <c r="E997" s="1"/>
       <c r="F997" s="1"/>
     </row>
-    <row r="998" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="998" spans="5:6" ht="17.25" customHeight="1">
       <c r="E998" s="1"/>
       <c r="F998" s="1"/>
     </row>
-    <row r="999" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="999" spans="5:6" ht="17.25" customHeight="1">
       <c r="E999" s="1"/>
       <c r="F999" s="1"/>
     </row>
-    <row r="1000" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1000" spans="5:6" ht="17.25" customHeight="1">
       <c r="E1000" s="1"/>
       <c r="F1000" s="1"/>
     </row>
-    <row r="1001" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1001" spans="5:6" ht="17.25" customHeight="1">
       <c r="E1001" s="1"/>
       <c r="F1001" s="1"/>
     </row>
-    <row r="1002" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1002" spans="5:6" ht="17.25" customHeight="1">
       <c r="E1002" s="1"/>
       <c r="F1002" s="1"/>
     </row>
-    <row r="1003" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1003" spans="5:6" ht="17.25" customHeight="1">
       <c r="E1003" s="1"/>
       <c r="F1003" s="1"/>
     </row>
-    <row r="1004" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1004" spans="5:6" ht="17.25" customHeight="1">
       <c r="E1004" s="1"/>
       <c r="F1004" s="1"/>
     </row>
-    <row r="1005" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1005" spans="5:6" ht="17.25" customHeight="1">
       <c r="E1005" s="1"/>
       <c r="F1005" s="1"/>
     </row>
-    <row r="1006" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1006" spans="5:6" ht="17.25" customHeight="1">
       <c r="E1006" s="1"/>
       <c r="F1006" s="1"/>
     </row>
-    <row r="1007" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1007" spans="5:6" ht="17.25" customHeight="1">
       <c r="E1007" s="1"/>
       <c r="F1007" s="1"/>
     </row>
-    <row r="1008" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1008" spans="5:6" ht="17.25" customHeight="1">
       <c r="E1008" s="1"/>
       <c r="F1008" s="1"/>
     </row>
-    <row r="1009" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1009" spans="5:6" ht="17.25" customHeight="1">
       <c r="E1009" s="1"/>
       <c r="F1009" s="1"/>
     </row>
-    <row r="1010" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1010" spans="5:6" ht="17.25" customHeight="1">
       <c r="E1010" s="1"/>
       <c r="F1010" s="1"/>
     </row>
-    <row r="1011" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1011" spans="5:6" ht="17.25" customHeight="1">
       <c r="E1011" s="1"/>
       <c r="F1011" s="1"/>
     </row>
-    <row r="1012" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1012" spans="5:6" ht="17.25" customHeight="1">
       <c r="E1012" s="1"/>
       <c r="F1012" s="1"/>
     </row>
-    <row r="1013" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1013" spans="5:6" ht="17.25" customHeight="1">
       <c r="E1013" s="1"/>
       <c r="F1013" s="1"/>
     </row>
-    <row r="1014" spans="5:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1014" spans="5:6" ht="17.25" customHeight="1">
       <c r="E1014" s="1"/>
       <c r="F1014" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A60"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="F3:W3"/>
     <mergeCell ref="X1:AB1"/>
@@ -7011,6 +6845,7 @@
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A10:A63"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
